--- a/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
+++ b/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,19 +540,19 @@
         <v>860</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1657027076379731</v>
+        <v>0.03072298391510259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8323574126196024</v>
+        <v>1.125244844700775</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5776850844124</v>
+        <v>1.200471148773608</v>
       </c>
       <c r="E2" t="n">
-        <v>8068.360030470056</v>
+        <v>9803.836308533559</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68973561095267</v>
+        <v>51.06164744027895</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5</v>
@@ -562,18 +562,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -582,51 +586,51 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>50.28774606163375</v>
+        <v>44.37825494668876</v>
       </c>
       <c r="O2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q2" t="n">
         <v>57</v>
       </c>
       <c r="R2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T2" t="n">
         <v>52</v>
       </c>
       <c r="U2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V2" t="n">
-        <v>60.31746031746032</v>
+        <v>59.89583333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>778</v>
+        <v>254</v>
       </c>
       <c r="B3" t="n">
-        <v>3.757917515251721</v>
+        <v>-0.3916425333854394</v>
       </c>
       <c r="C3" t="n">
-        <v>4.59824012167087</v>
+        <v>-0.4625483754357493</v>
       </c>
       <c r="D3" t="n">
-        <v>5.413021088640114</v>
+        <v>-0.3610186776840147</v>
       </c>
       <c r="E3" t="n">
-        <v>2640.554625652864</v>
+        <v>1439.614215093297</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9711884955178</v>
+        <v>7.49799070361092</v>
       </c>
       <c r="G3" t="n">
         <v>-0.25</v>
@@ -636,18 +640,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(189, 13)</t>
+          <t>(192, 13)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -656,72 +664,76 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.038377319547433</v>
+        <v>17.21017627950233</v>
       </c>
       <c r="O3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q3" t="n">
         <v>57</v>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="S3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="T3" t="n">
         <v>51</v>
       </c>
       <c r="U3" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="V3" t="n">
-        <v>58.73015873015873</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>254</v>
+        <v>146</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.6444096123483214</v>
+        <v>6.500646963432163</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4131454679386314</v>
+        <v>3.447682596519398</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.04666192350090711</v>
+        <v>4.359086285541517</v>
       </c>
       <c r="E4" t="n">
-        <v>1806.672847679238</v>
+        <v>1137.515500688098</v>
       </c>
       <c r="F4" t="n">
-        <v>9.559115596186443</v>
+        <v>5.924559899417179</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(189, 13)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -730,72 +742,76 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24.13740882571258</v>
+        <v>0.7184180195120943</v>
       </c>
       <c r="O4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q4" t="n">
         <v>57</v>
       </c>
       <c r="R4" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="S4" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U4" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="V4" t="n">
-        <v>55.55555555555556</v>
+        <v>59.375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>146</v>
+        <v>778</v>
       </c>
       <c r="B5" t="n">
-        <v>2.632387670311167</v>
+        <v>3.27527860381585</v>
       </c>
       <c r="C5" t="n">
-        <v>2.118673541390911</v>
+        <v>1.833207956806139</v>
       </c>
       <c r="D5" t="n">
-        <v>4.209236327173825</v>
+        <v>1.926050224159974</v>
       </c>
       <c r="E5" t="n">
-        <v>1607.253311209078</v>
+        <v>1122.246620052332</v>
       </c>
       <c r="F5" t="n">
-        <v>8.503985773593005</v>
+        <v>5.845034479439231</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 13)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -804,72 +820,76 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.013825446656652</v>
+        <v>2.188418672163412</v>
       </c>
       <c r="O5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q5" t="n">
         <v>57</v>
       </c>
       <c r="R5" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S5" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="T5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V5" t="n">
-        <v>60.31746031746032</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>342</v>
+        <v>954</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5453011261064512</v>
+        <v>-0.3352767611397775</v>
       </c>
       <c r="C6" t="n">
-        <v>5.052823386823922</v>
+        <v>1.265806794268597</v>
       </c>
       <c r="D6" t="n">
-        <v>3.460168036365444</v>
+        <v>0.4362459506426092</v>
       </c>
       <c r="E6" t="n">
-        <v>1245.960267082625</v>
+        <v>829.0165932196538</v>
       </c>
       <c r="F6" t="n">
-        <v>6.592382365516533</v>
+        <v>4.317794756352364</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(189, 45)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -878,13 +898,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.3046928144584011</v>
+        <v>2.411100948345956</v>
       </c>
       <c r="O6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q6" t="n">
         <v>57</v>
@@ -893,36 +913,36 @@
         <v>81</v>
       </c>
       <c r="S6" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="T6" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="U6" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="V6" t="n">
-        <v>58.73015873015873</v>
+        <v>54.6875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>682</v>
+        <v>288</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5630852487448587</v>
+        <v>-0.5580909448060055</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.09839284413799106</v>
+        <v>-0.5992852975120817</v>
       </c>
       <c r="D7" t="n">
-        <v>4.069291132775966</v>
+        <v>0.3465874001576115</v>
       </c>
       <c r="E7" t="n">
-        <v>988.0343999466634</v>
+        <v>722.8814660257383</v>
       </c>
       <c r="F7" t="n">
-        <v>5.227695237813034</v>
+        <v>3.76500763555072</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5</v>
@@ -932,18 +952,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>30</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(189, 29)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -952,31 +976,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>54.1308479149302</v>
+        <v>7.282496252087374</v>
       </c>
       <c r="O7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q7" t="n">
         <v>57</v>
       </c>
       <c r="R7" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="S7" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="T7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U7" t="n">
         <v>114</v>
       </c>
       <c r="V7" t="n">
-        <v>60.31746031746032</v>
+        <v>59.375</v>
       </c>
     </row>
     <row r="8">
@@ -984,19 +1008,19 @@
         <v>432</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.781951348249143</v>
+        <v>-1.100196634317709</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0395567970621596</v>
+        <v>0.03261273677241633</v>
       </c>
       <c r="D8" t="n">
-        <v>4.530099181526698</v>
+        <v>2.363073006705506</v>
       </c>
       <c r="E8" t="n">
-        <v>966.3257218539239</v>
+        <v>598.2768224747942</v>
       </c>
       <c r="F8" t="n">
-        <v>5.112834507163619</v>
+        <v>3.11602511705622</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5</v>
@@ -1006,18 +1030,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1026,72 +1054,76 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>128.252995360805</v>
+        <v>94.54626276233697</v>
       </c>
       <c r="O8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q8" t="n">
         <v>57</v>
       </c>
       <c r="R8" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S8" t="n">
         <v>52</v>
       </c>
       <c r="T8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
         <v>111</v>
       </c>
       <c r="V8" t="n">
-        <v>58.73015873015873</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>954</v>
+        <v>1332</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.7283440333344415</v>
+        <v>-1.115242081420737</v>
       </c>
       <c r="C9" t="n">
-        <v>1.216918505130592</v>
+        <v>-0.4178241437535075</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4345868980906265</v>
+        <v>0.9378784617594298</v>
       </c>
       <c r="E9" t="n">
-        <v>869.3386786145766</v>
+        <v>542.0940413185212</v>
       </c>
       <c r="F9" t="n">
-        <v>4.599675548225273</v>
+        <v>2.823406465200632</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 61)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1100,13 +1132,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.779772867971684</v>
+        <v>7.757403820269135</v>
       </c>
       <c r="O9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q9" t="n">
         <v>57</v>
@@ -1115,57 +1147,61 @@
         <v>80</v>
       </c>
       <c r="S9" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="T9" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="V9" t="n">
-        <v>55.02645502645503</v>
+        <v>60.41666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>288</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.8684413111053718</v>
+        <v>-0.7475531706677672</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6181691354925087</v>
+        <v>0.6773581274211415</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3390829987826307</v>
+        <v>3.548143046445918</v>
       </c>
       <c r="E10" t="n">
-        <v>816.3043584915828</v>
+        <v>493.0089576310904</v>
       </c>
       <c r="F10" t="n">
-        <v>4.319070679849644</v>
+        <v>2.567754987661929</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 10)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1174,31 +1210,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7.986875325647805</v>
+        <v>2.790838086549525</v>
       </c>
       <c r="O10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="n">
         <v>57</v>
       </c>
       <c r="R10" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="S10" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="T10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U10" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="V10" t="n">
-        <v>59.78835978835979</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1206,19 +1242,19 @@
         <v>1144</v>
       </c>
       <c r="B11" t="n">
-        <v>2.074659797153574</v>
+        <v>2.619694061862142</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5022042030207876</v>
+        <v>1.182536564706434</v>
       </c>
       <c r="D11" t="n">
-        <v>1.680574844563334</v>
+        <v>2.814689116051055</v>
       </c>
       <c r="E11" t="n">
-        <v>751.1658095391099</v>
+        <v>471.9306067544952</v>
       </c>
       <c r="F11" t="n">
-        <v>3.974422272693703</v>
+        <v>2.457971910179662</v>
       </c>
       <c r="G11" t="n">
         <v>-0.25</v>
@@ -1228,18 +1264,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(189, 73)</t>
+          <t>(192, 73)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1248,72 +1288,76 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6.913956611249609</v>
+        <v>1.078558907639237</v>
       </c>
       <c r="O11" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q11" t="n">
         <v>57</v>
       </c>
       <c r="R11" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U11" t="n">
         <v>115</v>
       </c>
       <c r="V11" t="n">
-        <v>60.84656084656085</v>
+        <v>59.89583333333334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>1056</v>
+        <v>138</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7819310351168969</v>
+        <v>-1.528425587993079</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3503971262022963</v>
+        <v>-0.7533659265544032</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2317800676771501</v>
+        <v>-0.09003739150781218</v>
       </c>
       <c r="E12" t="n">
-        <v>554.4924141687513</v>
+        <v>467.8983153679886</v>
       </c>
       <c r="F12" t="n">
-        <v>2.933822297189161</v>
+        <v>2.436970392541607</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1322,51 +1366,51 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.372849198241896</v>
+        <v>4.23477649657895</v>
       </c>
       <c r="O12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q12" t="n">
         <v>57</v>
       </c>
       <c r="R12" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="S12" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="T12" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="U12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="V12" t="n">
-        <v>54.4973544973545</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>90</v>
+        <v>1130</v>
       </c>
       <c r="B13" t="n">
-        <v>1.942109171794483</v>
+        <v>-0.1955198617445595</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4791432051095759</v>
+        <v>0.3044900903270141</v>
       </c>
       <c r="D13" t="n">
-        <v>1.368274456437313</v>
+        <v>2.727784854531916</v>
       </c>
       <c r="E13" t="n">
-        <v>482.9342193575817</v>
+        <v>445.4749549675342</v>
       </c>
       <c r="F13" t="n">
-        <v>2.555207509828475</v>
+        <v>2.320182057122574</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5</v>
@@ -1376,18 +1420,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 37)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1396,51 +1444,51 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.332868091584689</v>
+        <v>6.619893490230704</v>
       </c>
       <c r="O13" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q13" t="n">
         <v>57</v>
       </c>
       <c r="R13" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="S13" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="T13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U13" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="V13" t="n">
-        <v>55.02645502645503</v>
+        <v>58.85416666666666</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1130</v>
+        <v>872</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2729000170593142</v>
+        <v>1.306369797715353</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1914772198835965</v>
+        <v>0.85524541563187</v>
       </c>
       <c r="D14" t="n">
-        <v>2.593585364807292</v>
+        <v>1.711814225455332</v>
       </c>
       <c r="E14" t="n">
-        <v>444.3687320796474</v>
+        <v>441.2453279537203</v>
       </c>
       <c r="F14" t="n">
-        <v>2.351157312590727</v>
+        <v>2.29815274975896</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5</v>
@@ -1450,18 +1498,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>(189, 37)</t>
+          <t>(192, 24)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1470,51 +1522,51 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>11.27904454650036</v>
+        <v>1.687126651314519</v>
       </c>
       <c r="O14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="n">
         <v>57</v>
       </c>
       <c r="R14" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="S14" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="T14" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="V14" t="n">
-        <v>59.25925925925925</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>696</v>
+        <v>1056</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8526543990706194</v>
+        <v>0.7846150429936949</v>
       </c>
       <c r="C15" t="n">
-        <v>1.235273699159081</v>
+        <v>0.4566911948909405</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2372363541493517</v>
+        <v>0.1139341240164616</v>
       </c>
       <c r="E15" t="n">
-        <v>440.0707273829719</v>
+        <v>439.6418029921232</v>
       </c>
       <c r="F15" t="n">
-        <v>2.328416546999851</v>
+        <v>2.289801057250642</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5</v>
@@ -1524,18 +1576,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>25</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(189, 58)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1544,72 +1600,76 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.8849397899307115</v>
+        <v>4.013893595643889</v>
       </c>
       <c r="O15" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q15" t="n">
         <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="S15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="U15" t="n">
         <v>103</v>
       </c>
       <c r="V15" t="n">
-        <v>54.4973544973545</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>872</v>
+        <v>192</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6560771583091349</v>
+        <v>-1.351431952839844</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1839135447885434</v>
+        <v>-0.5382189578436329</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9924361221436053</v>
+        <v>0.5578443311184914</v>
       </c>
       <c r="E16" t="n">
-        <v>436.3852459092566</v>
+        <v>437.4920099187683</v>
       </c>
       <c r="F16" t="n">
-        <v>2.308916645022522</v>
+        <v>2.278604218326918</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>(189, 24)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1618,72 +1678,76 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>11.55435888464454</v>
+        <v>5.233600814538596</v>
       </c>
       <c r="O16" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q16" t="n">
         <v>57</v>
       </c>
       <c r="R16" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="S16" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="U16" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="V16" t="n">
-        <v>57.14285714285714</v>
+        <v>59.89583333333334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.564449297433176</v>
+        <v>2.000465847423982</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.8223544427728818</v>
+        <v>0.2699653779693226</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4101298692739601</v>
+        <v>0.9703334205345173</v>
       </c>
       <c r="E17" t="n">
-        <v>414.5877595293019</v>
+        <v>392.2842184954573</v>
       </c>
       <c r="F17" t="n">
-        <v>2.193586029255565</v>
+        <v>2.043146971330507</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>25</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1692,51 +1756,51 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.667445951722535</v>
+        <v>6.568181470894683</v>
       </c>
       <c r="O17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q17" t="n">
         <v>57</v>
       </c>
       <c r="R17" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="S17" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="T17" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="U17" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="V17" t="n">
-        <v>57.14285714285714</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>192</v>
+        <v>696</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.504530366176947</v>
+        <v>1.500486143583715</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.6521138798477373</v>
+        <v>1.37958292905636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6510995565612712</v>
+        <v>0.08108154883848519</v>
       </c>
       <c r="E18" t="n">
-        <v>388.202646702714</v>
+        <v>390.9076852469494</v>
       </c>
       <c r="F18" t="n">
-        <v>2.053982257686318</v>
+        <v>2.035977527327862</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5</v>
@@ -1746,18 +1810,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 58)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1766,51 +1834,51 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.149729397211886</v>
+        <v>0.4757920560241193</v>
       </c>
       <c r="O18" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
       </c>
       <c r="R18" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="U18" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="V18" t="n">
-        <v>60.31746031746032</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1332</v>
+        <v>811</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.10441814403466</v>
+        <v>-0.4690060260402478</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.670149848839801</v>
+        <v>0.1723676930952853</v>
       </c>
       <c r="D19" t="n">
-        <v>1.085416152651134</v>
+        <v>-0.09061351191444089</v>
       </c>
       <c r="E19" t="n">
-        <v>355.2481706166189</v>
+        <v>376.4383181666001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.879619950352481</v>
+        <v>1.960616240451042</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5</v>
@@ -1820,18 +1888,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(189, 61)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1840,72 +1912,76 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.804775608927733</v>
+        <v>10.37461553985763</v>
       </c>
       <c r="O19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q19" t="n">
         <v>57</v>
       </c>
       <c r="R19" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="T19" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="U19" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V19" t="n">
-        <v>59.78835978835979</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>32</v>
+        <v>682</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.7472641528912486</v>
+        <v>0.01903524970294143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2826422798440649</v>
+        <v>-0.2529893736830477</v>
       </c>
       <c r="D20" t="n">
-        <v>2.808167485305733</v>
+        <v>1.107639182582942</v>
       </c>
       <c r="E20" t="n">
-        <v>318.7768118532838</v>
+        <v>340.2161823565297</v>
       </c>
       <c r="F20" t="n">
-        <v>1.686649798165523</v>
+        <v>1.771959283106925</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(189, 10)</t>
+          <t>(192, 29)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1914,13 +1990,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.967436291187772</v>
+        <v>8.004085813212399</v>
       </c>
       <c r="O20" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P20" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q20" t="n">
         <v>57</v>
@@ -1929,57 +2005,61 @@
         <v>77</v>
       </c>
       <c r="S20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T20" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U20" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="V20" t="n">
-        <v>56.61375661375661</v>
+        <v>58.85416666666666</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>1116</v>
+        <v>864</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.40803034253905</v>
+        <v>-0.6852342251313093</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05890955908459475</v>
+        <v>-0.2446519422471579</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2072142549205101</v>
+        <v>0.9021899765552335</v>
       </c>
       <c r="E21" t="n">
-        <v>296.5456908304681</v>
+        <v>335.0629875363202</v>
       </c>
       <c r="F21" t="n">
-        <v>1.569024819208826</v>
+        <v>1.745119726751668</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(189, 27)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1988,13 +2068,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>25.63446889758061</v>
+        <v>8.133071214242284</v>
       </c>
       <c r="O21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P21" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q21" t="n">
         <v>57</v>
@@ -2003,57 +2083,61 @@
         <v>79</v>
       </c>
       <c r="S21" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="T21" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="U21" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="V21" t="n">
-        <v>58.2010582010582</v>
+        <v>59.89583333333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>235</v>
+        <v>1116</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.244959751608036</v>
+        <v>-1.035867976138612</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.6775452023649626</v>
+        <v>0.2344468300080766</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09170806449799196</v>
+        <v>-0.103923003322526</v>
       </c>
       <c r="E22" t="n">
-        <v>288.9418274349286</v>
+        <v>235.1538023627874</v>
       </c>
       <c r="F22" t="n">
-        <v>1.528792737750945</v>
+        <v>1.224759387306184</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(189, 49)</t>
+          <t>(192, 27)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2062,72 +2146,76 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.256370102562477</v>
+        <v>4.224039016710067</v>
       </c>
       <c r="O22" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P22" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q22" t="n">
         <v>57</v>
       </c>
       <c r="R22" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="S22" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="T22" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U22" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="V22" t="n">
-        <v>55.02645502645503</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>864</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.2271864652431009</v>
+        <v>-0.05315068107381791</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2446519267679982</v>
+        <v>-0.6159075839501452</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8688832495945505</v>
+        <v>-0.3121166099356153</v>
       </c>
       <c r="E23" t="n">
-        <v>286.709442874303</v>
+        <v>233.668241728126</v>
       </c>
       <c r="F23" t="n">
-        <v>1.516981179229116</v>
+        <v>1.21702209233399</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>20</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2136,51 +2224,51 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>7.200569107586302</v>
+        <v>2.975981663561561</v>
       </c>
       <c r="O23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P23" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q23" t="n">
         <v>57</v>
       </c>
       <c r="R23" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="T23" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="U23" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="V23" t="n">
-        <v>60.31746031746032</v>
+        <v>52.60416666666666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9229504394032233</v>
+        <v>-1.293788160820139</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4147706037710242</v>
+        <v>-0.6673896748144555</v>
       </c>
       <c r="D24" t="n">
-        <v>1.956293518946125</v>
+        <v>-0.1951605641334967</v>
       </c>
       <c r="E24" t="n">
-        <v>280.3048039004673</v>
+        <v>222.8992853238864</v>
       </c>
       <c r="F24" t="n">
-        <v>1.483094200531573</v>
+        <v>1.160933777728575</v>
       </c>
       <c r="G24" t="n">
         <v>-0.25</v>
@@ -2190,18 +2278,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>(189, 43)</t>
+          <t>(192, 7)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2210,72 +2302,76 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.57569747481507</v>
+        <v>2.739514142245806</v>
       </c>
       <c r="O24" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P24" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q24" t="n">
         <v>57</v>
       </c>
       <c r="R24" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="S24" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="T24" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="U24" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="V24" t="n">
-        <v>51.85185185185185</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>14</v>
+        <v>1496</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.060581954679199</v>
+        <v>-0.9150521960417977</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3660326921217933</v>
+        <v>-0.3630783308836746</v>
       </c>
       <c r="D25" t="n">
-        <v>1.284942936698613</v>
+        <v>0.8032047989089723</v>
       </c>
       <c r="E25" t="n">
-        <v>265.9832195579392</v>
+        <v>219.8388734498315</v>
       </c>
       <c r="F25" t="n">
-        <v>1.407318621999678</v>
+        <v>1.144994132551205</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>25</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(189, 8)</t>
+          <t>(192, 39)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2284,72 +2380,76 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.844789419878945</v>
+        <v>4.153573306797112</v>
       </c>
       <c r="O25" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P25" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q25" t="n">
         <v>57</v>
       </c>
       <c r="R25" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="S25" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="U25" t="n">
         <v>110</v>
       </c>
       <c r="V25" t="n">
-        <v>58.2010582010582</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>811</v>
+        <v>235</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.5320268094884415</v>
+        <v>-0.9769686194058197</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01179319286510292</v>
+        <v>-0.5167968694929747</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2421006964956299</v>
+        <v>-0.249929649878913</v>
       </c>
       <c r="E26" t="n">
-        <v>257.7544636730812</v>
+        <v>205.1911816054702</v>
       </c>
       <c r="F26" t="n">
-        <v>1.363780231074504</v>
+        <v>1.068704070861824</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 49)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2358,51 +2458,51 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>114.6413065294682</v>
+        <v>3.067938360211665</v>
       </c>
       <c r="O26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P26" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q26" t="n">
         <v>57</v>
       </c>
       <c r="R26" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="S26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T26" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="U26" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="V26" t="n">
-        <v>57.14285714285714</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" t="n">
-        <v>1.072499727888562</v>
+        <v>-0.3900731140239913</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1030702765157713</v>
+        <v>-0.3881601091945338</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9469557499175894</v>
+        <v>0.1157960790593826</v>
       </c>
       <c r="E27" t="n">
-        <v>241.8378617167514</v>
+        <v>201.1444033911306</v>
       </c>
       <c r="F27" t="n">
-        <v>1.279565405908737</v>
+        <v>1.047627100995472</v>
       </c>
       <c r="G27" t="n">
         <v>-0.25</v>
@@ -2412,18 +2512,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(189, 14)</t>
+          <t>(192, 7)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2432,51 +2536,51 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>13.41449474245802</v>
+        <v>3.69895611676684</v>
       </c>
       <c r="O27" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P27" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>57</v>
+      </c>
+      <c r="R27" t="n">
+        <v>72</v>
+      </c>
+      <c r="S27" t="n">
+        <v>71</v>
+      </c>
+      <c r="T27" t="n">
         <v>49</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>57</v>
-      </c>
-      <c r="R27" t="n">
-        <v>68</v>
-      </c>
-      <c r="S27" t="n">
-        <v>62</v>
-      </c>
-      <c r="T27" t="n">
-        <v>59</v>
       </c>
       <c r="U27" t="n">
         <v>106</v>
       </c>
       <c r="V27" t="n">
-        <v>56.08465608465608</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1496</v>
+        <v>60</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.087368137428359</v>
+        <v>1.097972549253034</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.573595791010173</v>
+        <v>0.01846471154984698</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5234535664656962</v>
+        <v>0.2599340410056952</v>
       </c>
       <c r="E28" t="n">
-        <v>235.8390140171935</v>
+        <v>190.7945347245726</v>
       </c>
       <c r="F28" t="n">
-        <v>1.247825470990442</v>
+        <v>0.9937215350238157</v>
       </c>
       <c r="G28" t="n">
         <v>-0.25</v>
@@ -2486,18 +2590,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(189, 39)</t>
+          <t>(192, 14)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2506,51 +2614,51 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.175443911108321</v>
+        <v>52.81733325977955</v>
       </c>
       <c r="O28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P28" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q28" t="n">
         <v>57</v>
       </c>
       <c r="R28" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S28" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="T28" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="U28" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V28" t="n">
-        <v>57.14285714285714</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.5084118817607367</v>
+        <v>-0.7695885145443685</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.5608658891240978</v>
+        <v>-0.4993487291023317</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.02738572265254561</v>
+        <v>0.7218519593009103</v>
       </c>
       <c r="E29" t="n">
-        <v>233.3117671632945</v>
+        <v>163.3242848934908</v>
       </c>
       <c r="F29" t="n">
-        <v>1.234453794514786</v>
+        <v>0.850647317153598</v>
       </c>
       <c r="G29" t="n">
         <v>-0.5</v>
@@ -2560,18 +2668,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(189, 13)</t>
+          <t>(192, 32)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2580,51 +2692,51 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.200978555573468</v>
+        <v>2.703513531881393</v>
       </c>
       <c r="O29" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P29" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q29" t="n">
         <v>57</v>
       </c>
       <c r="R29" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="S29" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="U29" t="n">
         <v>103</v>
       </c>
       <c r="V29" t="n">
-        <v>54.4973544973545</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>844</v>
+        <v>798</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.5857472198081575</v>
+        <v>-1.132847222790233</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1392730037891133</v>
+        <v>-0.7330450224764939</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7846137869390217</v>
+        <v>-0.3397854363811091</v>
       </c>
       <c r="E30" t="n">
-        <v>221.5216104687345</v>
+        <v>155.8483769249135</v>
       </c>
       <c r="F30" t="n">
-        <v>1.172072013062087</v>
+        <v>0.8117102964839243</v>
       </c>
       <c r="G30" t="n">
         <v>-0.5</v>
@@ -2634,18 +2746,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 11)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2654,51 +2770,51 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>9.415643959520212</v>
+        <v>2.107313018430533</v>
       </c>
       <c r="O30" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P30" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q30" t="n">
         <v>57</v>
       </c>
       <c r="R30" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="S30" t="n">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="T30" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="U30" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="V30" t="n">
-        <v>52.38095238095239</v>
+        <v>55.72916666666666</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>64</v>
+        <v>1390</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.294541284798947</v>
+        <v>-0.7133704257328179</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6754457317177051</v>
+        <v>-0.6902056876304496</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01805547990844256</v>
+        <v>-0.5075357067396302</v>
       </c>
       <c r="E31" t="n">
-        <v>205.5770010964421</v>
+        <v>152.7165517584675</v>
       </c>
       <c r="F31" t="n">
-        <v>1.087709000510276</v>
+        <v>0.7953987070753515</v>
       </c>
       <c r="G31" t="n">
         <v>-0.25</v>
@@ -2708,18 +2824,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(189, 7)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2728,51 +2848,51 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.610357352831525</v>
+        <v>2.152408218781912</v>
       </c>
       <c r="O31" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P31" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q31" t="n">
         <v>57</v>
       </c>
       <c r="R31" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="S31" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="T31" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="U31" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="V31" t="n">
-        <v>53.43915343915344</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>186</v>
+        <v>1068</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.6486707802220383</v>
+        <v>0.4204665540765825</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.7330375964093492</v>
+        <v>-0.2860599056181681</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4097719457975363</v>
+        <v>0.184268970399706</v>
       </c>
       <c r="E32" t="n">
-        <v>205.1507506338237</v>
+        <v>147.0061294443002</v>
       </c>
       <c r="F32" t="n">
-        <v>1.085453707057268</v>
+        <v>0.7656569241890635</v>
       </c>
       <c r="G32" t="n">
         <v>-0.5</v>
@@ -2782,18 +2902,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 29)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2802,72 +2926,76 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.480761303886956</v>
+        <v>3.676561479437318</v>
       </c>
       <c r="O32" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P32" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q32" t="n">
         <v>57</v>
       </c>
       <c r="R32" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="S32" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="T32" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="U32" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="V32" t="n">
-        <v>53.43915343915344</v>
+        <v>55.72916666666666</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.593407294572001</v>
+        <v>-0.6123704161688016</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3971037664160729</v>
+        <v>-0.3343443645533378</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4401375185894142</v>
+        <v>0.4015158176138374</v>
       </c>
       <c r="E33" t="n">
-        <v>197.6697256267358</v>
+        <v>146.7970279441367</v>
       </c>
       <c r="F33" t="n">
-        <v>1.045871564162624</v>
+        <v>0.7645678538757118</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(189, 7)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2876,51 +3004,51 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.633748789647068</v>
+        <v>3.286767581374145</v>
       </c>
       <c r="O33" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P33" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q33" t="n">
         <v>57</v>
       </c>
       <c r="R33" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="S33" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="T33" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="U33" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="V33" t="n">
-        <v>55.55555555555556</v>
+        <v>58.85416666666666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>44</v>
+        <v>1536</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1338442359206573</v>
+        <v>-0.2094438286759905</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4645654007996932</v>
+        <v>-0.09342276423966567</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2604643801828223</v>
+        <v>0.4869493660278871</v>
       </c>
       <c r="E34" t="n">
-        <v>188.6539300297523</v>
+        <v>146.0721746207203</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9981689419563614</v>
+        <v>0.760792576149585</v>
       </c>
       <c r="G34" t="n">
         <v>-0.5</v>
@@ -2930,18 +3058,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2950,51 +3082,51 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.148608011354557</v>
+        <v>9.143545979841237</v>
       </c>
       <c r="O34" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P34" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q34" t="n">
         <v>57</v>
       </c>
       <c r="R34" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="S34" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="T34" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="U34" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="V34" t="n">
-        <v>52.9100529100529</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>98</v>
+        <v>542</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.048517956206201</v>
+        <v>-0.915007258465915</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.7129510656398648</v>
+        <v>-0.4462065055412608</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8407638008998797</v>
+        <v>-0.3068330182991032</v>
       </c>
       <c r="E35" t="n">
-        <v>187.0910050912695</v>
+        <v>144.6458200327262</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9898994978374047</v>
+        <v>0.7533636460037823</v>
       </c>
       <c r="G35" t="n">
         <v>-0.5</v>
@@ -3004,18 +3136,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(189, 32)</t>
+          <t>(192, 9)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3024,72 +3160,76 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.388453633839487</v>
+        <v>2.68837441105869</v>
       </c>
       <c r="O35" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P35" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q35" t="n">
         <v>57</v>
       </c>
       <c r="R35" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="S35" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="T35" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="U35" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="V35" t="n">
-        <v>53.43915343915344</v>
+        <v>54.6875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1390</v>
+        <v>186</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.7723413622164901</v>
+        <v>-0.4512024880350569</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.643133822060832</v>
+        <v>-0.7112111059613129</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4001459847582433</v>
+        <v>-0.4737276157297247</v>
       </c>
       <c r="E36" t="n">
-        <v>186.2307768960416</v>
+        <v>138.2081899243294</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9853480259049818</v>
+        <v>0.7198343225225491</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3098,72 +3238,76 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.532104193723745</v>
+        <v>2.012124693342043</v>
       </c>
       <c r="O36" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P36" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>57</v>
+      </c>
+      <c r="R36" t="n">
+        <v>61</v>
+      </c>
+      <c r="S36" t="n">
+        <v>82</v>
+      </c>
+      <c r="T36" t="n">
         <v>49</v>
       </c>
-      <c r="Q36" t="n">
-        <v>57</v>
-      </c>
-      <c r="R36" t="n">
-        <v>59</v>
-      </c>
-      <c r="S36" t="n">
-        <v>59</v>
-      </c>
-      <c r="T36" t="n">
-        <v>71</v>
-      </c>
       <c r="U36" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="V36" t="n">
-        <v>55.55555555555556</v>
+        <v>52.60416666666666</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1024</v>
+        <v>1124</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5137689191377993</v>
+        <v>0.5956072368445723</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1703049953336033</v>
+        <v>0.2230619715109501</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5666870676575684</v>
+        <v>2.19494953770419</v>
       </c>
       <c r="E37" t="n">
-        <v>185.4618373895381</v>
+        <v>137.1680863413083</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9812795629076088</v>
+        <v>0.7144171163609806</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>20</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(189, 11)</t>
+          <t>(192, 74)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3172,72 +3316,76 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>6.761895362995205</v>
+        <v>2.202774150706859</v>
       </c>
       <c r="O37" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P37" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q37" t="n">
         <v>57</v>
       </c>
       <c r="R37" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="S37" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="T37" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="U37" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="V37" t="n">
-        <v>55.02645502645503</v>
+        <v>55.72916666666666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>878</v>
+        <v>823</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.07251863766485314</v>
+        <v>-1.111595930889667</v>
       </c>
       <c r="C38" t="n">
-        <v>0.03440310800532586</v>
+        <v>-0.7331476648729942</v>
       </c>
       <c r="D38" t="n">
-        <v>1.008337720911459</v>
+        <v>-0.1352264800405438</v>
       </c>
       <c r="E38" t="n">
-        <v>170.0279797116879</v>
+        <v>131.5276661563231</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8996189402734808</v>
+        <v>0.6850399278975162</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(189, 8)</t>
+          <t>(192, 20)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3246,72 +3394,76 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>25.14935081255487</v>
+        <v>1.934381927024467</v>
       </c>
       <c r="O38" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P38" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q38" t="n">
         <v>57</v>
       </c>
       <c r="R38" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="S38" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="T38" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="U38" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V38" t="n">
-        <v>58.2010582010582</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1536</v>
+        <v>154</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.1281308902614526</v>
+        <v>-0.1223285181970408</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1240738707999041</v>
+        <v>-0.2854698633863967</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5403056869058979</v>
+        <v>0.4648241662384184</v>
       </c>
       <c r="E39" t="n">
-        <v>165.7816578043518</v>
+        <v>130.3205766018223</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8771516285944538</v>
+        <v>0.6787530031344912</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3320,72 +3472,76 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>8.069591872482563</v>
+        <v>3.377669555317535</v>
       </c>
       <c r="O39" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P39" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q39" t="n">
         <v>57</v>
       </c>
       <c r="R39" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="S39" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="T39" t="n">
         <v>62</v>
       </c>
       <c r="U39" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V39" t="n">
-        <v>57.14285714285714</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.2269618496705709</v>
+        <v>-0.1222985623372099</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.008835066536527734</v>
+        <v>-0.4092962187738092</v>
       </c>
       <c r="D40" t="n">
-        <v>2.255492468502553</v>
+        <v>-0.1378684187818408</v>
       </c>
       <c r="E40" t="n">
-        <v>158.9885937013283</v>
+        <v>128.7200949271994</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8412094904832187</v>
+        <v>0.6704171610791634</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(189, 46)</t>
+          <t>(192, 13)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3394,72 +3550,76 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>96.21258125282009</v>
+        <v>2.63797545720709</v>
       </c>
       <c r="O40" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P40" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q40" t="n">
         <v>57</v>
       </c>
       <c r="R40" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="T40" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="U40" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="V40" t="n">
-        <v>60.31746031746032</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>542</v>
+        <v>164</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.047389199798529</v>
+        <v>0.2986519317519654</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4442476493928427</v>
+        <v>0.004467875069471034</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1306227709560862</v>
+        <v>0.5722095672442589</v>
       </c>
       <c r="E41" t="n">
-        <v>151.0465527632324</v>
+        <v>125.6543763772813</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7991881098583725</v>
+        <v>0.6544498769650069</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(189, 9)</t>
+          <t>(192, 43)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3468,51 +3628,51 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.798969810984099</v>
+        <v>145.4790010438876</v>
       </c>
       <c r="O41" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P41" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q41" t="n">
         <v>57</v>
       </c>
       <c r="R41" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="S41" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="T41" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="V41" t="n">
-        <v>55.02645502645503</v>
+        <v>51.04166666666666</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>154</v>
+        <v>1024</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.3464044845909706</v>
+        <v>0.8195211063022828</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2802053985935271</v>
+        <v>-0.005412240857374968</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5148806370634325</v>
+        <v>0.3301329688547099</v>
       </c>
       <c r="E42" t="n">
-        <v>147.384649151527</v>
+        <v>123.6232423854833</v>
       </c>
       <c r="F42" t="n">
-        <v>0.779812958473688</v>
+        <v>0.6438710540910586</v>
       </c>
       <c r="G42" t="n">
         <v>-0.25</v>
@@ -3522,18 +3682,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 11)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3542,72 +3706,76 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.783004761463943</v>
+        <v>119.9657058986372</v>
       </c>
       <c r="O42" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P42" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>57</v>
+      </c>
+      <c r="R42" t="n">
+        <v>70</v>
+      </c>
+      <c r="S42" t="n">
+        <v>73</v>
+      </c>
+      <c r="T42" t="n">
         <v>49</v>
       </c>
-      <c r="Q42" t="n">
-        <v>57</v>
-      </c>
-      <c r="R42" t="n">
-        <v>83</v>
-      </c>
-      <c r="S42" t="n">
-        <v>46</v>
-      </c>
-      <c r="T42" t="n">
-        <v>60</v>
-      </c>
       <c r="U42" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="V42" t="n">
-        <v>58.2010582010582</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>240</v>
+        <v>878</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.3908197475337281</v>
+        <v>0.3423541023806635</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.5496780332174444</v>
+        <v>0.09827295118341084</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1295688615105291</v>
+        <v>0.7810459446665088</v>
       </c>
       <c r="E43" t="n">
-        <v>141.4990839362095</v>
+        <v>120.2419438983756</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7486724017788864</v>
+        <v>0.6262601244707063</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>20</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 8)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3616,51 +3784,51 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.362019867151436</v>
+        <v>5.372660197228547</v>
       </c>
       <c r="O43" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P43" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q43" t="n">
         <v>57</v>
       </c>
       <c r="R43" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S43" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="T43" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="U43" t="n">
         <v>110</v>
       </c>
       <c r="V43" t="n">
-        <v>58.2010582010582</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>504</v>
+        <v>844</v>
       </c>
       <c r="B44" t="n">
-        <v>1.830738578807982</v>
+        <v>-0.2179730319512584</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4667259135233232</v>
+        <v>0.02090404183251053</v>
       </c>
       <c r="D44" t="n">
-        <v>1.071236165211452</v>
+        <v>0.1142576318811337</v>
       </c>
       <c r="E44" t="n">
-        <v>139.7214124803579</v>
+        <v>114.5227906781407</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7392667327003064</v>
+        <v>0.5964728681153163</v>
       </c>
       <c r="G44" t="n">
         <v>-0.5</v>
@@ -3670,18 +3838,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>15</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>(189, 33)</t>
+          <t>(192, 20)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3690,51 +3862,51 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.583941905259914</v>
+        <v>27.53385354346477</v>
       </c>
       <c r="O44" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q44" t="n">
         <v>57</v>
       </c>
       <c r="R44" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="S44" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="T44" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="U44" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="V44" t="n">
-        <v>54.4973544973545</v>
+        <v>51.04166666666666</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>361</v>
+        <v>848</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.061272120100501</v>
+        <v>0.1739427072939813</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.7314805330370718</v>
+        <v>0.04617846134612406</v>
       </c>
       <c r="D45" t="n">
-        <v>0.06286818280656395</v>
+        <v>-0.007408189789882916</v>
       </c>
       <c r="E45" t="n">
-        <v>135.4957788012487</v>
+        <v>111.6165367437528</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7169088825462895</v>
+        <v>0.5813361288737128</v>
       </c>
       <c r="G45" t="n">
         <v>-0.25</v>
@@ -3744,18 +3916,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>20</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(189, 38)</t>
+          <t>(192, 10)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3764,51 +3940,51 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.980079236790784</v>
+        <v>11.58890209694063</v>
       </c>
       <c r="O45" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P45" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q45" t="n">
         <v>57</v>
       </c>
       <c r="R45" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S45" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="T45" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="U45" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="V45" t="n">
-        <v>58.73015873015873</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>798</v>
+        <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.251392146855928</v>
+        <v>-0.549664284291757</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.7222681495439341</v>
+        <v>0.3641104179446307</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2480768249634097</v>
+        <v>0.7489315586362428</v>
       </c>
       <c r="E46" t="n">
-        <v>134.6623678603909</v>
+        <v>108.0986236448929</v>
       </c>
       <c r="F46" t="n">
-        <v>0.712499300848629</v>
+        <v>0.5630136648171508</v>
       </c>
       <c r="G46" t="n">
         <v>-0.5</v>
@@ -3818,18 +3994,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>20</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>(189, 11)</t>
+          <t>(192, 8)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3838,19 +4018,19 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.986474761899063</v>
+        <v>0.5462717820470787</v>
       </c>
       <c r="O46" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P46" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q46" t="n">
         <v>57</v>
       </c>
       <c r="R46" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S46" t="n">
         <v>47</v>
@@ -3859,51 +4039,55 @@
         <v>66</v>
       </c>
       <c r="U46" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V46" t="n">
-        <v>56.08465608465608</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>823</v>
+        <v>496</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.197840265356739</v>
+        <v>0.6995061174352452</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.7199957191716748</v>
+        <v>-0.4243367081180199</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1177019390229868</v>
+        <v>0.4752629169002497</v>
       </c>
       <c r="E47" t="n">
-        <v>133.1712322091289</v>
+        <v>93.90113936123885</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7046096942281951</v>
+        <v>0.489068434173119</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>20</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 9)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3912,51 +4096,51 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.978630393856813</v>
+        <v>2.152548023342575</v>
       </c>
       <c r="O47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P47" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q47" t="n">
         <v>57</v>
       </c>
       <c r="R47" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="S47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T47" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U47" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="V47" t="n">
-        <v>58.2010582010582</v>
+        <v>58.85416666666666</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>148</v>
+        <v>1108</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.8225076328934062</v>
+        <v>-0.2302820856791598</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2986824019321453</v>
+        <v>-0.2775573355552001</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7766671882845934</v>
+        <v>-0.2317864337394972</v>
       </c>
       <c r="E48" t="n">
-        <v>124.2271395675434</v>
+        <v>86.26687923394735</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6572864527383249</v>
+        <v>0.4493066626768091</v>
       </c>
       <c r="G48" t="n">
         <v>-0.5</v>
@@ -3966,18 +4150,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 54)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3986,51 +4174,51 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.200619951113314</v>
+        <v>2.618788643355642</v>
       </c>
       <c r="O48" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P48" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q48" t="n">
         <v>57</v>
       </c>
       <c r="R48" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="S48" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T48" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="U48" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V48" t="n">
-        <v>58.73015873015873</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>430</v>
+        <v>240</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1257282210838684</v>
+        <v>-0.07292724001461323</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03078394335760294</v>
+        <v>-0.4427615348546498</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4932510939584768</v>
+        <v>0.1845357681927314</v>
       </c>
       <c r="E49" t="n">
-        <v>122.0997686452072</v>
+        <v>84.93442434752259</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6460305219323134</v>
+        <v>0.4423667934766802</v>
       </c>
       <c r="G49" t="n">
         <v>-0.25</v>
@@ -4040,18 +4228,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>20</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4060,51 +4252,51 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>19.98595733586413</v>
+        <v>1.999108456026788</v>
       </c>
       <c r="O49" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P49" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q49" t="n">
         <v>57</v>
       </c>
       <c r="R49" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="S49" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="T49" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="U49" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="V49" t="n">
-        <v>55.02645502645503</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1006</v>
+        <v>1095</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.137075638932446</v>
+        <v>-1.074657389703972</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.7226490330684667</v>
+        <v>-0.3639101297323895</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.03300432021942508</v>
+        <v>0.3701992613493286</v>
       </c>
       <c r="E50" t="n">
-        <v>116.0684176315162</v>
+        <v>84.50562931402743</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6141186118069638</v>
+        <v>0.4401334860105595</v>
       </c>
       <c r="G50" t="n">
         <v>-0.25</v>
@@ -4114,18 +4306,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>20</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 74)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4134,72 +4330,76 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.849815863171271</v>
+        <v>2.209456538992808</v>
       </c>
       <c r="O50" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q50" t="n">
         <v>57</v>
       </c>
       <c r="R50" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="S50" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="T50" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="U50" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="V50" t="n">
-        <v>55.02645502645503</v>
+        <v>59.89583333333334</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1108</v>
+        <v>832</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.8351482828163739</v>
+        <v>-0.460361933421529</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4403753258319946</v>
+        <v>-0.2836992300285432</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1914153082903836</v>
+        <v>-0.1126371522174425</v>
       </c>
       <c r="E51" t="n">
-        <v>111.4958345924264</v>
+        <v>83.85179362033958</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5899250507535789</v>
+        <v>0.436728091772602</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>15</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(189, 54)</t>
+          <t>(192, 7)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4208,72 +4408,76 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.339596058519042</v>
+        <v>2.539405276950038</v>
       </c>
       <c r="O51" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P51" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q51" t="n">
         <v>57</v>
       </c>
       <c r="R51" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="S51" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="T51" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="U51" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="V51" t="n">
-        <v>58.2010582010582</v>
+        <v>52.60416666666666</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>940</v>
+        <v>884</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.7652442323378937</v>
+        <v>-0.2315476727242813</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2512785547218694</v>
+        <v>-0.1760471206633566</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3015541734922529</v>
+        <v>-0.1098015098839464</v>
       </c>
       <c r="E52" t="n">
-        <v>110.6737248776238</v>
+        <v>76.11163440365016</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5855752639027716</v>
+        <v>0.3964147625190113</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>15</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>(189, 22)</t>
+          <t>(192, 44)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4282,72 +4486,76 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.330382967026066</v>
+        <v>3.251753740846743</v>
       </c>
       <c r="O52" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P52" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q52" t="n">
         <v>57</v>
       </c>
       <c r="R52" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="S52" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="T52" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="U52" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V52" t="n">
-        <v>53.96825396825397</v>
+        <v>52.60416666666666</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1095</v>
+        <v>736</v>
       </c>
       <c r="B53" t="n">
-        <v>-1.236266054991789</v>
+        <v>0.6927525658439668</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.5149716412861918</v>
+        <v>0.04159186834854268</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1149790251640208</v>
+        <v>0.3763865717065732</v>
       </c>
       <c r="E53" t="n">
-        <v>110.4860241652004</v>
+        <v>74.76099723177938</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5845821384402139</v>
+        <v>0.3893801939155176</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>20</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K53" t="b">
         <v>0</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>(189, 74)</t>
+          <t>(192, 14)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4356,51 +4564,51 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.135173457280411</v>
+        <v>8.361930814275647</v>
       </c>
       <c r="O53" t="n">
+        <v>84</v>
+      </c>
+      <c r="P53" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>57</v>
+      </c>
+      <c r="R53" t="n">
         <v>83</v>
       </c>
-      <c r="P53" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>57</v>
-      </c>
-      <c r="R53" t="n">
-        <v>106</v>
-      </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="T53" t="n">
         <v>71</v>
       </c>
       <c r="U53" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V53" t="n">
-        <v>60.31746031746032</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1125</v>
+        <v>1006</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.156576219106155</v>
+        <v>-0.8071853036271969</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.3669384119591297</v>
+        <v>-0.5849557720510427</v>
       </c>
       <c r="D54" t="n">
-        <v>0.589359325337503</v>
+        <v>0.1616793847576844</v>
       </c>
       <c r="E54" t="n">
-        <v>109.6968782125528</v>
+        <v>72.49305478014622</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5804067630293801</v>
+        <v>0.3775679936465949</v>
       </c>
       <c r="G54" t="n">
         <v>-0.25</v>
@@ -4410,18 +4618,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>20</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K54" t="b">
         <v>0</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>(189, 55)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4430,51 +4642,51 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.581755259501224</v>
+        <v>1.645464172996739</v>
       </c>
       <c r="O54" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P54" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q54" t="n">
         <v>57</v>
       </c>
       <c r="R54" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="S54" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="T54" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="U54" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="V54" t="n">
-        <v>59.25925925925925</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>360</v>
+        <v>158</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6029111168685688</v>
+        <v>-1.080858522533784</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1894964938561807</v>
+        <v>-0.4477793513540382</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3640890919228679</v>
+        <v>0.141562241204975</v>
       </c>
       <c r="E55" t="n">
-        <v>100.7957784006346</v>
+        <v>70.90075902381571</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5333109968287543</v>
+        <v>0.3692747865823735</v>
       </c>
       <c r="G55" t="n">
         <v>-0.5</v>
@@ -4484,18 +4696,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>(189, 57)</t>
+          <t>(192, 8)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4504,51 +4720,51 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.814358123340864</v>
+        <v>1.824680248130524</v>
       </c>
       <c r="O55" t="n">
+        <v>84</v>
+      </c>
+      <c r="P55" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>57</v>
+      </c>
+      <c r="R55" t="n">
         <v>83</v>
       </c>
-      <c r="P55" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>57</v>
-      </c>
-      <c r="R55" t="n">
-        <v>72</v>
-      </c>
       <c r="S55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T55" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="U55" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V55" t="n">
-        <v>58.2010582010582</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>496</v>
+        <v>1202</v>
       </c>
       <c r="B56" t="n">
-        <v>0.3427845044125962</v>
+        <v>-0.07506974945226574</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.436486651453203</v>
+        <v>-0.140209896490808</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4871664140024309</v>
+        <v>0.2953874545774244</v>
       </c>
       <c r="E56" t="n">
-        <v>94.45164195055585</v>
+        <v>65.98167061030719</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4997441373045283</v>
+        <v>0.3436545344286833</v>
       </c>
       <c r="G56" t="n">
         <v>-0.5</v>
@@ -4558,18 +4774,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>20</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K56" t="b">
         <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>(189, 9)</t>
+          <t>(192, 26)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4578,51 +4798,51 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.144924216217658</v>
+        <v>3.451000557233938</v>
       </c>
       <c r="O56" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P56" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q56" t="n">
         <v>57</v>
       </c>
       <c r="R56" t="n">
+        <v>89</v>
+      </c>
+      <c r="S56" t="n">
+        <v>22</v>
+      </c>
+      <c r="T56" t="n">
         <v>81</v>
-      </c>
-      <c r="S56" t="n">
-        <v>29</v>
-      </c>
-      <c r="T56" t="n">
-        <v>79</v>
       </c>
       <c r="U56" t="n">
         <v>112</v>
       </c>
       <c r="V56" t="n">
-        <v>59.25925925925925</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.5945886004139453</v>
+        <v>-1.005126433051936</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.617017509058371</v>
+        <v>-0.7980966770906942</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3569987212569701</v>
+        <v>-0.3931481142415456</v>
       </c>
       <c r="E57" t="n">
-        <v>78.83065752683282</v>
+        <v>64.03522538404985</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4170934260678985</v>
+        <v>0.3335167988752596</v>
       </c>
       <c r="G57" t="n">
         <v>-0.5</v>
@@ -4632,18 +4852,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>15</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K57" t="b">
         <v>0</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4652,72 +4876,76 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.675983128427626</v>
+        <v>1.417890223639359</v>
       </c>
       <c r="O57" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P57" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q57" t="n">
         <v>57</v>
       </c>
       <c r="R57" t="n">
+        <v>74</v>
+      </c>
+      <c r="S57" t="n">
+        <v>38</v>
+      </c>
+      <c r="T57" t="n">
         <v>80</v>
       </c>
-      <c r="S57" t="n">
-        <v>33</v>
-      </c>
-      <c r="T57" t="n">
-        <v>76</v>
-      </c>
       <c r="U57" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V57" t="n">
-        <v>58.2010582010582</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>318</v>
+        <v>430</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.8179318844844363</v>
+        <v>0.1235709812197629</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5603264201362482</v>
+        <v>0.0733073036683291</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1520022975990348</v>
+        <v>0.3444237023182931</v>
       </c>
       <c r="E58" t="n">
-        <v>76.63336364541038</v>
+        <v>62.10918943588985</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4054675325153989</v>
+        <v>0.3234853616452596</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K58" t="b">
         <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4726,51 +4954,51 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.723627367806083</v>
+        <v>3.412730320962749</v>
       </c>
       <c r="O58" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q58" t="n">
         <v>57</v>
       </c>
       <c r="R58" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="T58" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="U58" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="V58" t="n">
-        <v>59.78835978835979</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>848</v>
+        <v>940</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.121272973032012</v>
+        <v>-0.6507508910405071</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.141232120073079</v>
+        <v>-0.2774611362598249</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1203978965816924</v>
+        <v>0.03247448148428721</v>
       </c>
       <c r="E59" t="n">
-        <v>70.35580035155303</v>
+        <v>60.83155284566249</v>
       </c>
       <c r="F59" t="n">
-        <v>0.372252911912979</v>
+        <v>0.3168310044044921</v>
       </c>
       <c r="G59" t="n">
         <v>-0.25</v>
@@ -4780,18 +5008,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>15</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K59" t="b">
         <v>0</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>(189, 10)</t>
+          <t>(192, 22)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4800,72 +5032,76 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>3.635752488317536</v>
+        <v>2.141893270803158</v>
       </c>
       <c r="O59" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P59" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q59" t="n">
         <v>57</v>
       </c>
       <c r="R59" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="S59" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="T59" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U59" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V59" t="n">
-        <v>55.02645502645503</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>956</v>
+        <v>224</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.07754232750428713</v>
+        <v>-0.1235096083413256</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.02885550079046524</v>
+        <v>-0.4558008853885558</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.1361285347739564</v>
+        <v>-0.003426211699270236</v>
       </c>
       <c r="E60" t="n">
-        <v>69.15942339907147</v>
+        <v>54.62621199372549</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3659228751273623</v>
+        <v>0.2845115208006536</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>15</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K60" t="b">
         <v>0</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 20)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4874,51 +5110,51 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>13.68121727585039</v>
+        <v>1.624201334225397</v>
       </c>
       <c r="O60" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P60" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q60" t="n">
         <v>57</v>
       </c>
       <c r="R60" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="S60" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="T60" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="U60" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="V60" t="n">
-        <v>57.14285714285714</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>204</v>
+        <v>1022</v>
       </c>
       <c r="B61" t="n">
-        <v>0.5124455389970666</v>
+        <v>-0.1022349249035366</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5707378224416501</v>
+        <v>0.04910473801101205</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.08804089288273484</v>
+        <v>-0.002663192200922804</v>
       </c>
       <c r="E61" t="n">
-        <v>68.15590210213321</v>
+        <v>54.19977019673939</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3606132386356254</v>
+        <v>0.2822904697746844</v>
       </c>
       <c r="G61" t="n">
         <v>-0.5</v>
@@ -4928,18 +5164,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>15</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>(189, 26)</t>
+          <t>(192, 11)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4948,72 +5188,76 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.631836938881851</v>
+        <v>4.74874199942537</v>
       </c>
       <c r="O61" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P61" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q61" t="n">
         <v>57</v>
       </c>
       <c r="R61" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S61" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="T61" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="U61" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="V61" t="n">
-        <v>58.2010582010582</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.171809125004805</v>
+        <v>-0.7141103827111379</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.8055377196421756</v>
+        <v>-0.3702779233332622</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3736321698840048</v>
+        <v>-0.03914348656964118</v>
       </c>
       <c r="E62" t="n">
-        <v>67.63078590540562</v>
+        <v>52.69319552844443</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3578348460603472</v>
+        <v>0.274443726710648</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K62" t="b">
         <v>0</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5022,51 +5266,51 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.444218609923443</v>
+        <v>1.741183066600597</v>
       </c>
       <c r="O62" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P62" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q62" t="n">
         <v>57</v>
       </c>
       <c r="R62" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="S62" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="T62" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U62" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="V62" t="n">
-        <v>57.14285714285714</v>
+        <v>54.6875</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>1504</v>
+        <v>956</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.3300720892384956</v>
+        <v>0.1142610414128922</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3887233060010034</v>
+        <v>-0.1608897528500884</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.02377669797769045</v>
+        <v>-0.2172742017541436</v>
       </c>
       <c r="E63" t="n">
-        <v>66.21893076317721</v>
+        <v>50.21845956652646</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3503647130326837</v>
+        <v>0.261554476908992</v>
       </c>
       <c r="G63" t="n">
         <v>-0.25</v>
@@ -5076,18 +5320,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>(189, 13)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5096,72 +5344,76 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.901321602342462</v>
+        <v>2.625675173686788</v>
       </c>
       <c r="O63" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P63" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q63" t="n">
         <v>57</v>
       </c>
       <c r="R63" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="S63" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="T63" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="U63" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V63" t="n">
-        <v>57.67195767195767</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>1406</v>
+        <v>924</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.8509907976522263</v>
+        <v>-0.2454222438213884</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5974945452931361</v>
+        <v>0.1049371125804835</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2983059889677518</v>
+        <v>0.7661578948030441</v>
       </c>
       <c r="E64" t="n">
-        <v>61.3769707802113</v>
+        <v>50.14298693098743</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3247458771439751</v>
+        <v>0.2611613902655596</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>15</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K64" t="b">
         <v>0</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>(189, 10)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5170,72 +5422,76 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.543512706019186</v>
+        <v>1.488741912593192</v>
       </c>
       <c r="O64" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P64" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q64" t="n">
         <v>57</v>
       </c>
       <c r="R64" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="S64" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="T64" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="U64" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="V64" t="n">
-        <v>56.61375661375661</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>352</v>
+        <v>552</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.8950799075225122</v>
+        <v>-0.2414490607218497</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.6045080506095194</v>
+        <v>0.09775521834521612</v>
       </c>
       <c r="D65" t="n">
-        <v>0.001683974252118787</v>
+        <v>0.03505363728139221</v>
       </c>
       <c r="E65" t="n">
-        <v>60.06192812893127</v>
+        <v>48.2517085667306</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3177879795181549</v>
+        <v>0.2513109821183885</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>15</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K65" t="b">
         <v>0</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>(189, 15)</t>
+          <t>(192, 32)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5244,72 +5500,76 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.525696852503011</v>
+        <v>1.570819096643008</v>
       </c>
       <c r="O65" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P65" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q65" t="n">
         <v>57</v>
       </c>
       <c r="R65" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="S65" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="T65" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U65" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V65" t="n">
-        <v>56.61375661375661</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>1296</v>
+        <v>830</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.8124018397429787</v>
+        <v>-0.9646904204928635</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2794353760551786</v>
+        <v>-0.3639086960868852</v>
       </c>
       <c r="D66" t="n">
-        <v>0.01240980514633454</v>
+        <v>0.03173275385625601</v>
       </c>
       <c r="E66" t="n">
-        <v>58.97171100399257</v>
+        <v>48.00585367570858</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3120196349417596</v>
+        <v>0.2500304878943155</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K66" t="b">
         <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 7)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5318,51 +5578,51 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.116607493820492</v>
+        <v>1.687069285738144</v>
       </c>
       <c r="O66" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P66" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q66" t="n">
         <v>57</v>
       </c>
       <c r="R66" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="S66" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="T66" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="U66" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="V66" t="n">
-        <v>59.25925925925925</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>286</v>
+        <v>1262</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.8271004337044705</v>
+        <v>0.2502138120323616</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3704318007040059</v>
+        <v>0.04636092236140371</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.01587776789955313</v>
+        <v>0.1975626136500455</v>
       </c>
       <c r="E67" t="n">
-        <v>58.09644506764639</v>
+        <v>47.22158467023445</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3073885982415153</v>
+        <v>0.2459457534908044</v>
       </c>
       <c r="G67" t="n">
         <v>-0.25</v>
@@ -5372,18 +5632,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K67" t="b">
         <v>0</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 9)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5392,51 +5656,51 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.829811581125927</v>
+        <v>4.3050228719254</v>
       </c>
       <c r="O67" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P67" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q67" t="n">
         <v>57</v>
       </c>
       <c r="R67" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="S67" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="T67" t="n">
         <v>76</v>
       </c>
       <c r="U67" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V67" t="n">
-        <v>55.02645502645503</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>638</v>
+        <v>1486</v>
       </c>
       <c r="B68" t="n">
-        <v>0.5504204329029676</v>
+        <v>0.7842912128482032</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.08124392542022846</v>
+        <v>0.02624685453438701</v>
       </c>
       <c r="D68" t="n">
-        <v>0.03838854634960815</v>
+        <v>0.04555932702020849</v>
       </c>
       <c r="E68" t="n">
-        <v>57.7478872270563</v>
+        <v>43.03698220003071</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3055443768627318</v>
+        <v>0.2241509489584933</v>
       </c>
       <c r="G68" t="n">
         <v>-0.5</v>
@@ -5446,18 +5710,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>15</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K68" t="b">
         <v>0</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>(189, 12)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5466,72 +5734,76 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>4.760827351489051</v>
+        <v>7.54010710749452</v>
       </c>
       <c r="O68" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P68" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q68" t="n">
         <v>57</v>
       </c>
       <c r="R68" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="S68" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="T68" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="U68" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="V68" t="n">
-        <v>54.4973544973545</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>1219</v>
+        <v>824</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.5991837272799007</v>
+        <v>-0.3321590550547862</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3412339739766512</v>
+        <v>-0.4881214781868639</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2430869780497145</v>
+        <v>-0.05746038000924111</v>
       </c>
       <c r="E69" t="n">
-        <v>57.70680587527661</v>
+        <v>42.10720238615482</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3053270152131038</v>
+        <v>0.219308345761223</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>15</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K69" t="b">
         <v>0</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>(189, 40)</t>
+          <t>(192, 20)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5540,72 +5812,76 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.894773201082246</v>
+        <v>1.449290505666433</v>
       </c>
       <c r="O69" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P69" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q69" t="n">
         <v>57</v>
       </c>
       <c r="R69" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="S69" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T69" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="U69" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="V69" t="n">
-        <v>57.14285714285714</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>1022</v>
+        <v>361</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.2701600861298792</v>
+        <v>-0.7356722152022095</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.02152507971917984</v>
+        <v>-0.6015924633379024</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1208479591830334</v>
+        <v>-0.03532381730999949</v>
       </c>
       <c r="E70" t="n">
-        <v>57.35998121021163</v>
+        <v>42.07074696702443</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3034919640751938</v>
+        <v>0.2191184737865856</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>15</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K70" t="b">
         <v>0</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>(189, 11)</t>
+          <t>(192, 38)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5614,51 +5890,51 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>15.0994583079183</v>
+        <v>1.364230749452576</v>
       </c>
       <c r="O70" t="n">
+        <v>84</v>
+      </c>
+      <c r="P70" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>57</v>
+      </c>
+      <c r="R70" t="n">
+        <v>79</v>
+      </c>
+      <c r="S70" t="n">
+        <v>30</v>
+      </c>
+      <c r="T70" t="n">
         <v>83</v>
       </c>
-      <c r="P70" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>57</v>
-      </c>
-      <c r="R70" t="n">
-        <v>77</v>
-      </c>
-      <c r="S70" t="n">
-        <v>59</v>
-      </c>
-      <c r="T70" t="n">
-        <v>53</v>
-      </c>
       <c r="U70" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="V70" t="n">
-        <v>53.96825396825397</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>320</v>
+        <v>208</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.3562796831265743</v>
+        <v>-0.364007142073331</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4982909638831067</v>
+        <v>0.08332233481389352</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.05065479112754408</v>
+        <v>-0.1022181730965838</v>
       </c>
       <c r="E71" t="n">
-        <v>52.40614539790403</v>
+        <v>40.93497508055231</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2772811925815028</v>
+        <v>0.2132029952112099</v>
       </c>
       <c r="G71" t="n">
         <v>-0.5</v>
@@ -5668,18 +5944,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>10</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K71" t="b">
         <v>0</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 13)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5688,72 +5968,76 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.556464420748657</v>
+        <v>1.558773655195984</v>
       </c>
       <c r="O71" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P71" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q71" t="n">
         <v>57</v>
       </c>
       <c r="R71" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="S71" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="T71" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="U71" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="V71" t="n">
-        <v>56.08465608465608</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3673378806855757</v>
+        <v>1.092827549090898</v>
       </c>
       <c r="C72" t="n">
-        <v>0.03225635723346315</v>
+        <v>0.06644312532568421</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4789937845332929</v>
+        <v>0.04295429093393097</v>
       </c>
       <c r="E72" t="n">
-        <v>51.24911943020757</v>
+        <v>40.15195254767539</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2711593620645903</v>
+        <v>0.209124752852476</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>15</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K72" t="b">
         <v>0</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>(189, 14)</t>
+          <t>(192, 19)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5762,51 +6046,51 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>7.406385138346812</v>
+        <v>2.147424986820072</v>
       </c>
       <c r="O72" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P72" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q72" t="n">
         <v>57</v>
       </c>
       <c r="R72" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="S72" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="T72" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="U72" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="V72" t="n">
-        <v>57.14285714285714</v>
+        <v>48.95833333333333</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>208</v>
+        <v>1344</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.4872661897157877</v>
+        <v>-0.792625548500395</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0666145171538389</v>
+        <v>-0.5394496992495685</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.0314953530061491</v>
+        <v>-0.07527671151629912</v>
       </c>
       <c r="E73" t="n">
-        <v>51.23566089647196</v>
+        <v>39.1743243389447</v>
       </c>
       <c r="F73" t="n">
-        <v>0.271088152891386</v>
+        <v>0.204032939265337</v>
       </c>
       <c r="G73" t="n">
         <v>-0.5</v>
@@ -5816,18 +6100,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K73" t="b">
         <v>0</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>(189, 13)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5836,72 +6124,76 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3.069505634415059</v>
+        <v>1.378224215435041</v>
       </c>
       <c r="O73" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P73" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q73" t="n">
         <v>57</v>
       </c>
       <c r="R73" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S73" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="T73" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="U73" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="V73" t="n">
-        <v>53.96825396825397</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>364</v>
+        <v>188</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.07312057453880272</v>
+        <v>-0.4021966602733306</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5223623781015325</v>
+        <v>-0.6214677744222903</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1635806999447313</v>
+        <v>-0.1686908290516204</v>
       </c>
       <c r="E74" t="n">
-        <v>50.68135063736815</v>
+        <v>38.96513584714481</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2681552943776093</v>
+        <v>0.2029434158705459</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>10</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K74" t="b">
         <v>0</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>(189, 38)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5910,51 +6202,51 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.513351086562148</v>
+        <v>1.326555010932304</v>
       </c>
       <c r="O74" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P74" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q74" t="n">
         <v>57</v>
       </c>
       <c r="R74" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="S74" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T74" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="V74" t="n">
-        <v>56.61375661375661</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>563</v>
+        <v>1118</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.1932930965549539</v>
+        <v>-0.4688124061871841</v>
       </c>
       <c r="C75" t="n">
-        <v>0.01900643993086589</v>
+        <v>-0.3582154197102425</v>
       </c>
       <c r="D75" t="n">
-        <v>0.04482141491888664</v>
+        <v>0.09360741851874299</v>
       </c>
       <c r="E75" t="n">
-        <v>50.6242043992716</v>
+        <v>37.96197914602877</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2678529333294793</v>
+        <v>0.1977186413855665</v>
       </c>
       <c r="G75" t="n">
         <v>-0.5</v>
@@ -5964,18 +6256,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>15</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K75" t="b">
         <v>0</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>(189, 61)</t>
+          <t>(192, 14)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5984,72 +6280,76 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>13.09274615886872</v>
+        <v>1.551954579580911</v>
       </c>
       <c r="O75" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P75" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q75" t="n">
         <v>57</v>
       </c>
       <c r="R75" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="S75" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="T75" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="U75" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V75" t="n">
-        <v>58.2010582010582</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>592</v>
+        <v>394</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.7520142077467011</v>
+        <v>-0.4185471016258063</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.2013703504582149</v>
+        <v>-0.3198273614448189</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2425869323598742</v>
+        <v>0.1001774120848834</v>
       </c>
       <c r="E76" t="n">
-        <v>49.90646072765466</v>
+        <v>37.87271633308316</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2640553477653686</v>
+        <v>0.1972537309014748</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>15</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K76" t="b">
         <v>0</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>(189, 12)</t>
+          <t>(192, 15)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6058,51 +6358,51 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.311292090243251</v>
+        <v>1.616750643254479</v>
       </c>
       <c r="O76" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P76" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q76" t="n">
         <v>57</v>
       </c>
       <c r="R76" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S76" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="T76" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="U76" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="V76" t="n">
-        <v>57.14285714285714</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>1486</v>
+        <v>563</v>
       </c>
       <c r="B77" t="n">
-        <v>0.4945018001678415</v>
+        <v>0.2407023548016539</v>
       </c>
       <c r="C77" t="n">
-        <v>0.001682298571251408</v>
+        <v>0.1055045105979878</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0623413233836078</v>
+        <v>0.1119629386830082</v>
       </c>
       <c r="E77" t="n">
-        <v>48.06139002920301</v>
+        <v>34.79926784990485</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2542930689375821</v>
+        <v>0.1812461867182544</v>
       </c>
       <c r="G77" t="n">
         <v>-0.5</v>
@@ -6112,18 +6412,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>15</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K77" t="b">
         <v>0</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 61)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6132,72 +6436,76 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>150.1581078906948</v>
+        <v>0.7178998859003406</v>
       </c>
       <c r="O77" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P77" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q77" t="n">
         <v>57</v>
       </c>
       <c r="R77" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="S77" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="T77" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="U77" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V77" t="n">
-        <v>57.67195767195767</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>624</v>
+        <v>916</v>
       </c>
       <c r="B78" t="n">
-        <v>0.4368087829739309</v>
+        <v>-0.7018617749843173</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.2924890946205367</v>
+        <v>-0.232064187862783</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.03217405718951966</v>
+        <v>0.04972504902747469</v>
       </c>
       <c r="E78" t="n">
-        <v>47.95360254692091</v>
+        <v>34.35620700397126</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2537227647985233</v>
+        <v>0.1789385781456837</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>15</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K78" t="b">
         <v>0</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>(189, 25)</t>
+          <t>(192, 31)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6206,51 +6514,51 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.867460597557296</v>
+        <v>1.771073640416625</v>
       </c>
       <c r="O78" t="n">
+        <v>84</v>
+      </c>
+      <c r="P78" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>57</v>
+      </c>
+      <c r="R78" t="n">
+        <v>85</v>
+      </c>
+      <c r="S78" t="n">
+        <v>24</v>
+      </c>
+      <c r="T78" t="n">
         <v>83</v>
       </c>
-      <c r="P78" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>57</v>
-      </c>
-      <c r="R78" t="n">
-        <v>71</v>
-      </c>
-      <c r="S78" t="n">
-        <v>41</v>
-      </c>
-      <c r="T78" t="n">
-        <v>77</v>
-      </c>
       <c r="U78" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V78" t="n">
-        <v>57.14285714285714</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>1344</v>
+        <v>320</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.193572698208975</v>
+        <v>-0.2363878489368273</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7100611232132445</v>
+        <v>-0.4961326203871458</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.1712110645410639</v>
+        <v>-0.2276753889010868</v>
       </c>
       <c r="E79" t="n">
-        <v>46.93862560291237</v>
+        <v>34.21448230810179</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2483525164175258</v>
+        <v>0.1782004286880302</v>
       </c>
       <c r="G79" t="n">
         <v>-0.5</v>
@@ -6260,18 +6568,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>15</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K79" t="b">
         <v>0</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>(189, 16)</t>
+          <t>(192, 20)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6280,72 +6592,76 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.349762165957846</v>
+        <v>1.359179020619478</v>
       </c>
       <c r="O79" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P79" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q79" t="n">
         <v>57</v>
       </c>
       <c r="R79" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S79" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="T79" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U79" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V79" t="n">
-        <v>57.67195767195767</v>
+        <v>55.20833333333334</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>1124</v>
+        <v>586</v>
       </c>
       <c r="B80" t="n">
-        <v>0.2239636526494579</v>
+        <v>-0.7457885346845592</v>
       </c>
       <c r="C80" t="n">
-        <v>0.05470181124288786</v>
+        <v>-0.1750767357301807</v>
       </c>
       <c r="D80" t="n">
-        <v>0.672947654099606</v>
+        <v>-0.05669602234503704</v>
       </c>
       <c r="E80" t="n">
-        <v>45.04126653496942</v>
+        <v>32.92007935630872</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2383135795501028</v>
+        <v>0.1714587466474412</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>10</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K80" t="b">
         <v>0</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>(189, 74)</t>
+          <t>(192, 23)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6354,51 +6670,51 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3.356593943332864</v>
+        <v>1.979334838134546</v>
       </c>
       <c r="O80" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P80" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q80" t="n">
         <v>57</v>
       </c>
       <c r="R80" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="S80" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="T80" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="U80" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="V80" t="n">
-        <v>55.02645502645503</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.276430114938695</v>
+        <v>-0.4835537374252573</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.2545752232539576</v>
+        <v>-0.02459951893825476</v>
       </c>
       <c r="D81" t="n">
-        <v>0.08538640955236569</v>
+        <v>0.4938559183090551</v>
       </c>
       <c r="E81" t="n">
-        <v>44.68918973531902</v>
+        <v>32.70617566748427</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2364507393403123</v>
+        <v>0.1703446649348139</v>
       </c>
       <c r="G81" t="n">
         <v>-0.5</v>
@@ -6408,18 +6724,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>15</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K81" t="b">
         <v>0</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>(189, 19)</t>
+          <t>(192, 16)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6428,72 +6748,76 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.928804996487954</v>
+        <v>7.924715290668169</v>
       </c>
       <c r="O81" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P81" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q81" t="n">
         <v>57</v>
       </c>
       <c r="R81" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="S81" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="T81" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="U81" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V81" t="n">
-        <v>55.55555555555556</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>473</v>
+        <v>1456</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.4750568166066114</v>
+        <v>-0.4918923917449959</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.321436074237598</v>
+        <v>-0.3122289813324571</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2123405509849096</v>
+        <v>0.05317102748393817</v>
       </c>
       <c r="E82" t="n">
-        <v>43.68884707226474</v>
+        <v>31.52826524720387</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2311579210172737</v>
+        <v>0.1642097148291868</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>15</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K82" t="b">
         <v>0</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 13)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6502,51 +6826,51 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.719141190252365</v>
+        <v>1.525927202940648</v>
       </c>
       <c r="O82" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P82" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q82" t="n">
         <v>57</v>
       </c>
       <c r="R82" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T82" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="U82" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V82" t="n">
-        <v>59.78835978835979</v>
+        <v>57.29166666666666</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>830</v>
+        <v>360</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.048712576632294</v>
+        <v>0.6602124789003131</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.3668134865010885</v>
+        <v>-0.1013494492751386</v>
       </c>
       <c r="D83" t="n">
-        <v>0.02460306190889469</v>
+        <v>0.07053371588092498</v>
       </c>
       <c r="E83" t="n">
-        <v>43.15296056422204</v>
+        <v>31.38042797901611</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2283225426678415</v>
+        <v>0.1634397290573756</v>
       </c>
       <c r="G83" t="n">
         <v>-0.25</v>
@@ -6556,18 +6880,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K83" t="b">
         <v>0</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>(189, 7)</t>
+          <t>(192, 57)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6576,72 +6904,76 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.622448604182289</v>
+        <v>2.612635591276646</v>
       </c>
       <c r="O83" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P83" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q83" t="n">
         <v>57</v>
       </c>
       <c r="R83" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S83" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="T83" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="U83" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="V83" t="n">
-        <v>53.43915343915344</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>776</v>
+        <v>1159</v>
       </c>
       <c r="B84" t="n">
-        <v>1.095034579369805</v>
+        <v>-0.8878661462785091</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1171414444914814</v>
+        <v>-0.3692429082202351</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1980099593943625</v>
+        <v>0.1425998676156204</v>
       </c>
       <c r="E84" t="n">
-        <v>43.01215344026912</v>
+        <v>31.14412694263203</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2275775314299953</v>
+        <v>0.1622089944928752</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K84" t="b">
         <v>0</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>(189, 19)</t>
+          <t>(192, 22)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6650,51 +6982,51 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0.9427584525521613</v>
+        <v>1.439301584083845</v>
       </c>
       <c r="O84" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P84" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q84" t="n">
         <v>57</v>
       </c>
       <c r="R84" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S84" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="T84" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="U84" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="V84" t="n">
-        <v>49.73544973544973</v>
+        <v>54.16666666666666</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>884</v>
+        <v>638</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.3910897488149871</v>
+        <v>0.4134594009285965</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.1937929371756759</v>
+        <v>-0.002067738638907883</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.08166698859275034</v>
+        <v>0.05673451935124177</v>
       </c>
       <c r="E85" t="n">
-        <v>42.44132913722052</v>
+        <v>30.41699491198486</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2245572970223308</v>
+        <v>0.1584218484999211</v>
       </c>
       <c r="G85" t="n">
         <v>-0.5</v>
@@ -6704,18 +7036,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>15</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K85" t="b">
         <v>0</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>(189, 44)</t>
+          <t>(192, 12)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6724,51 +7060,51 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.158748612281812</v>
+        <v>77.61599271733624</v>
       </c>
       <c r="O85" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P85" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q85" t="n">
         <v>57</v>
       </c>
       <c r="R85" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="S85" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="T85" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="U85" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V85" t="n">
-        <v>52.38095238095239</v>
+        <v>53.64583333333334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>1244</v>
+        <v>1406</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02049994119823765</v>
+        <v>-0.5694675922635994</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.2277678179254259</v>
+        <v>-0.4253596344810229</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.1598567650960872</v>
+        <v>0.2546828833011428</v>
       </c>
       <c r="E86" t="n">
-        <v>41.67805460709613</v>
+        <v>29.50497714020867</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2205188074449531</v>
+        <v>0.1536717559385868</v>
       </c>
       <c r="G86" t="n">
         <v>-0.5</v>
@@ -6778,18 +7114,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>10</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K86" t="b">
         <v>0</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>(189, 31)</t>
+          <t>(192, 10)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6798,51 +7138,51 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1.968173684296145</v>
+        <v>1.361274891836129</v>
       </c>
       <c r="O86" t="n">
+        <v>84</v>
+      </c>
+      <c r="P86" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>57</v>
+      </c>
+      <c r="R86" t="n">
+        <v>67</v>
+      </c>
+      <c r="S86" t="n">
+        <v>42</v>
+      </c>
+      <c r="T86" t="n">
         <v>83</v>
       </c>
-      <c r="P86" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>57</v>
-      </c>
-      <c r="R86" t="n">
-        <v>70</v>
-      </c>
-      <c r="S86" t="n">
-        <v>62</v>
-      </c>
-      <c r="T86" t="n">
-        <v>57</v>
-      </c>
       <c r="U86" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="V86" t="n">
-        <v>53.43915343915344</v>
+        <v>55.72916666666666</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>704</v>
+        <v>888</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.3480839229087479</v>
+        <v>-0.027579760354798</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.3997034969201794</v>
+        <v>-0.1574502889186158</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1724372633174787</v>
+        <v>0.1356102696434043</v>
       </c>
       <c r="E87" t="n">
-        <v>41.35006789767235</v>
+        <v>29.43905479678554</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2187834280300124</v>
+        <v>0.1533284103999247</v>
       </c>
       <c r="G87" t="n">
         <v>-0.5</v>
@@ -6852,18 +7192,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K87" t="b">
         <v>0</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 33)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6872,72 +7216,76 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1.547364308082857</v>
+        <v>1.973821079992927</v>
       </c>
       <c r="O87" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P87" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q87" t="n">
         <v>57</v>
       </c>
       <c r="R87" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="S87" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="T87" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U87" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="V87" t="n">
-        <v>59.25925925925925</v>
+        <v>56.77083333333334</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>1264</v>
+        <v>533</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.85560621056827</v>
+        <v>-0.2929427424830857</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.5690626146128516</v>
+        <v>-0.5591751877170337</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1141570798162238</v>
+        <v>0.002043066094340418</v>
       </c>
       <c r="E88" t="n">
-        <v>40.71306785842731</v>
+        <v>29.18871468194493</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2154130574519963</v>
+        <v>0.1520245556351298</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>15</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K88" t="b">
         <v>0</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>(189, 9)</t>
+          <t>(192, 25)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6946,51 +7294,51 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1.378540167497293</v>
+        <v>1.271872856619061</v>
       </c>
       <c r="O88" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P88" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q88" t="n">
         <v>57</v>
       </c>
       <c r="R88" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="S88" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="T88" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="U88" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="V88" t="n">
-        <v>55.55555555555556</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>832</v>
+        <v>1422</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.363411307225702</v>
+        <v>-0.9136422222244294</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1107840594017973</v>
+        <v>-0.3273017653187252</v>
       </c>
       <c r="D89" t="n">
-        <v>0.01513970592897323</v>
+        <v>0.1225452168408113</v>
       </c>
       <c r="E89" t="n">
-        <v>40.46959842082671</v>
+        <v>29.16706826229813</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2141248593694535</v>
+        <v>0.1519118138661361</v>
       </c>
       <c r="G89" t="n">
         <v>-0.25</v>
@@ -7000,18 +7348,22 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K89" t="b">
         <v>0</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>(189, 7)</t>
+          <t>(192, 19)</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7020,13 +7372,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.932812902196105</v>
+        <v>1.464133805444664</v>
       </c>
       <c r="O89" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P89" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q89" t="n">
         <v>57</v>
@@ -7035,57 +7387,61 @@
         <v>66</v>
       </c>
       <c r="S89" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="T89" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="U89" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V89" t="n">
-        <v>52.38095238095239</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>222</v>
+        <v>488</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.224527843230076</v>
+        <v>-0.0350485202970475</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.4213272742362041</v>
+        <v>0.06272732084234078</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1286576861451904</v>
+        <v>0.6650656805949272</v>
       </c>
       <c r="E90" t="n">
-        <v>40.40818930101884</v>
+        <v>28.20466781316079</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2137999433916341</v>
+        <v>0.1468993115268791</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>10</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K90" t="b">
         <v>0</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>(189, 20)</t>
+          <t>(192, 27)</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7094,549 +7450,31 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1.507443871938311</v>
+        <v>1.341871285975958</v>
       </c>
       <c r="O90" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P90" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q90" t="n">
         <v>57</v>
       </c>
       <c r="R90" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="S90" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="T90" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="U90" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="V90" t="n">
-        <v>54.4973544973545</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0.02073686737120425</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.0015337644385761</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.571205472500755</v>
-      </c>
-      <c r="E91" t="n">
-        <v>39.97688295447523</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.2115178992300277</v>
-      </c>
-      <c r="G91" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>10</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>(189, 22)</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N91" t="n">
-        <v>136.9076825033148</v>
-      </c>
-      <c r="O91" t="n">
-        <v>83</v>
-      </c>
-      <c r="P91" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>57</v>
-      </c>
-      <c r="R91" t="n">
-        <v>73</v>
-      </c>
-      <c r="S91" t="n">
-        <v>63</v>
-      </c>
-      <c r="T91" t="n">
-        <v>53</v>
-      </c>
-      <c r="U91" t="n">
-        <v>100</v>
-      </c>
-      <c r="V91" t="n">
-        <v>52.9100529100529</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B92" t="n">
-        <v>-0.5921044814595069</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.009590671693821946</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.6183619829828031</v>
-      </c>
-      <c r="E92" t="n">
-        <v>39.52849841534857</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.2091454942611035</v>
-      </c>
-      <c r="G92" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>15</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>(189, 16)</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N92" t="n">
-        <v>22.80717898995848</v>
-      </c>
-      <c r="O92" t="n">
-        <v>83</v>
-      </c>
-      <c r="P92" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>57</v>
-      </c>
-      <c r="R92" t="n">
-        <v>71</v>
-      </c>
-      <c r="S92" t="n">
-        <v>59</v>
-      </c>
-      <c r="T92" t="n">
-        <v>59</v>
-      </c>
-      <c r="U92" t="n">
-        <v>103</v>
-      </c>
-      <c r="V92" t="n">
-        <v>54.4973544973545</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>224</v>
-      </c>
-      <c r="B93" t="n">
-        <v>-0.1788789469899547</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.3118296127260896</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.1547477650550299</v>
-      </c>
-      <c r="E93" t="n">
-        <v>39.19143436156091</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.2073620865691053</v>
-      </c>
-      <c r="G93" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>10</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="b">
-        <v>0</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>(189, 20)</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N93" t="n">
-        <v>1.664985229453662</v>
-      </c>
-      <c r="O93" t="n">
-        <v>83</v>
-      </c>
-      <c r="P93" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>57</v>
-      </c>
-      <c r="R93" t="n">
-        <v>65</v>
-      </c>
-      <c r="S93" t="n">
-        <v>52</v>
-      </c>
-      <c r="T93" t="n">
-        <v>72</v>
-      </c>
-      <c r="U93" t="n">
-        <v>103</v>
-      </c>
-      <c r="V93" t="n">
-        <v>54.4973544973545</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>915</v>
-      </c>
-      <c r="B94" t="n">
-        <v>-0.6253126675770084</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.440037188104122</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.04990248318490453</v>
-      </c>
-      <c r="E94" t="n">
-        <v>38.99605581954711</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.2063283376695614</v>
-      </c>
-      <c r="G94" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>10</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="b">
-        <v>0</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>(189, 31)</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N94" t="n">
-        <v>1.468888410451209</v>
-      </c>
-      <c r="O94" t="n">
-        <v>83</v>
-      </c>
-      <c r="P94" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>57</v>
-      </c>
-      <c r="R94" t="n">
-        <v>98</v>
-      </c>
-      <c r="S94" t="n">
-        <v>14</v>
-      </c>
-      <c r="T94" t="n">
-        <v>77</v>
-      </c>
-      <c r="U94" t="n">
-        <v>111</v>
-      </c>
-      <c r="V94" t="n">
-        <v>58.73015873015873</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>1118</v>
-      </c>
-      <c r="B95" t="n">
-        <v>-0.682555376676668</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.4013004860584003</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.190296191501904</v>
-      </c>
-      <c r="E95" t="n">
-        <v>38.37893117977708</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.2030631279353285</v>
-      </c>
-      <c r="G95" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>10</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="b">
-        <v>0</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>(189, 14)</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>1.506012663801701</v>
-      </c>
-      <c r="O95" t="n">
-        <v>83</v>
-      </c>
-      <c r="P95" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>57</v>
-      </c>
-      <c r="R95" t="n">
-        <v>77</v>
-      </c>
-      <c r="S95" t="n">
-        <v>32</v>
-      </c>
-      <c r="T95" t="n">
-        <v>80</v>
-      </c>
-      <c r="U95" t="n">
-        <v>107</v>
-      </c>
-      <c r="V95" t="n">
-        <v>56.61375661375661</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>1096</v>
-      </c>
-      <c r="B96" t="n">
-        <v>-0.4187546360811933</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.1087202857207629</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.1321678206877764</v>
-      </c>
-      <c r="E96" t="n">
-        <v>37.40358357416082</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.1979025585934435</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>10</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="b">
-        <v>0</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>(189, 74)</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N96" t="n">
-        <v>0.8202910090002549</v>
-      </c>
-      <c r="O96" t="n">
-        <v>83</v>
-      </c>
-      <c r="P96" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>57</v>
-      </c>
-      <c r="R96" t="n">
-        <v>103</v>
-      </c>
-      <c r="S96" t="n">
-        <v>40</v>
-      </c>
-      <c r="T96" t="n">
-        <v>46</v>
-      </c>
-      <c r="U96" t="n">
-        <v>106</v>
-      </c>
-      <c r="V96" t="n">
-        <v>56.08465608465608</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>789</v>
-      </c>
-      <c r="B97" t="n">
-        <v>-0.6899203432700409</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.05327934914781594</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.3195465656366999</v>
-      </c>
-      <c r="E97" t="n">
-        <v>34.81777991601285</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.1842210577566818</v>
-      </c>
-      <c r="G97" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>10</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="b">
-        <v>0</v>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>(189, 31)</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>4.457644672902944</v>
-      </c>
-      <c r="O97" t="n">
-        <v>83</v>
-      </c>
-      <c r="P97" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>57</v>
-      </c>
-      <c r="R97" t="n">
-        <v>95</v>
-      </c>
-      <c r="S97" t="n">
-        <v>11</v>
-      </c>
-      <c r="T97" t="n">
-        <v>83</v>
-      </c>
-      <c r="U97" t="n">
-        <v>110</v>
-      </c>
-      <c r="V97" t="n">
-        <v>58.2010582010582</v>
+        <v>56.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
+++ b/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>% ROI 100</t>
+          <t>% roi_100</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -545,22 +545,22 @@
         <v>860</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.01440714299954607</v>
+        <v>-0.01440714299954692</v>
       </c>
       <c r="C2" t="n">
-        <v>1.127483283172962</v>
+        <v>1.127483283172959</v>
       </c>
       <c r="D2" t="n">
-        <v>1.186257825024301</v>
+        <v>1.186257825024297</v>
       </c>
       <c r="E2" t="n">
-        <v>34.93830479936172</v>
+        <v>34.93830479936162</v>
       </c>
       <c r="F2" t="n">
-        <v>8059.733334261385</v>
+        <v>15120.22078984523</v>
       </c>
       <c r="G2" t="n">
-        <v>40.0981757923452</v>
+        <v>71.32179617851524</v>
       </c>
       <c r="H2" t="n">
         <v>-0.5</v>
@@ -581,7 +581,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>(201, 31)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -590,31 +590,31 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>34.56431956977754</v>
+        <v>62.25751986122732</v>
       </c>
       <c r="P2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T2" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="U2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="V2" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="W2" t="n">
-        <v>59.70149253731343</v>
+        <v>59.43396226415094</v>
       </c>
     </row>
     <row r="3">
@@ -622,22 +622,22 @@
         <v>432</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.7939613376487187</v>
+        <v>-0.7939613499550131</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03261274730908952</v>
+        <v>0.03261273677241519</v>
       </c>
       <c r="D3" t="n">
-        <v>2.363073037620655</v>
+        <v>2.363073006705503</v>
       </c>
       <c r="E3" t="n">
-        <v>5.288584788546756</v>
+        <v>5.28858472948063</v>
       </c>
       <c r="F3" t="n">
-        <v>1172.784544639944</v>
+        <v>1600.358117915456</v>
       </c>
       <c r="G3" t="n">
-        <v>5.834748978308181</v>
+        <v>7.548859046771017</v>
       </c>
       <c r="H3" t="n">
         <v>-0.5</v>
@@ -658,7 +658,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>177.9100722796811</v>
+        <v>230.4696586014843</v>
       </c>
       <c r="P3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="U3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="V3" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="W3" t="n">
-        <v>58.70646766169154</v>
+        <v>58.01886792452831</v>
       </c>
     </row>
     <row r="4">
@@ -699,22 +699,22 @@
         <v>146</v>
       </c>
       <c r="B4" t="n">
-        <v>4.377337833343947</v>
+        <v>4.37733775852683</v>
       </c>
       <c r="C4" t="n">
-        <v>2.247064929702806</v>
+        <v>2.24706489160916</v>
       </c>
       <c r="D4" t="n">
-        <v>4.321306137648223</v>
+        <v>4.321306079130742</v>
       </c>
       <c r="E4" t="n">
-        <v>4.454701611156757</v>
+        <v>4.45470155302961</v>
       </c>
       <c r="F4" t="n">
-        <v>1017.36707213083</v>
+        <v>1128.249343001611</v>
       </c>
       <c r="G4" t="n">
-        <v>5.061527722043931</v>
+        <v>5.321930863215147</v>
       </c>
       <c r="H4" t="n">
         <v>-0.5</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>(201, 31)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -744,54 +744,54 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1.252506216059081</v>
+        <v>1.368392155957733</v>
       </c>
       <c r="P4" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q4" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S4" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="U4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="W4" t="n">
-        <v>59.20398009950249</v>
+        <v>58.49056603773585</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>682</v>
+        <v>1536</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1635441624542409</v>
+        <v>0.1739890298160674</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2439101372756677</v>
+        <v>-0.2301817734925082</v>
       </c>
       <c r="D5" t="n">
-        <v>1.129502923907369</v>
+        <v>0.4132464390111742</v>
       </c>
       <c r="E5" t="n">
-        <v>2.801562834467349</v>
+        <v>0.4808518048053221</v>
       </c>
       <c r="F5" t="n">
-        <v>637.530264528903</v>
+        <v>478.1157967186381</v>
       </c>
       <c r="G5" t="n">
-        <v>3.171792360840314</v>
+        <v>2.255263192069048</v>
       </c>
       <c r="H5" t="n">
         <v>-0.5</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>(201, 29)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -821,54 +821,54 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>14.00393823835025</v>
+        <v>10.79774878718819</v>
       </c>
       <c r="P5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S5" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V5" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="W5" t="n">
-        <v>59.20398009950249</v>
+        <v>57.54716981132076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>288</v>
+        <v>682</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2492399216360792</v>
+        <v>0.1635441466506455</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.4478210367301</v>
+        <v>-0.2439101427985219</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5291422953615397</v>
+        <v>1.129502910787259</v>
       </c>
       <c r="E6" t="n">
-        <v>1.772531250897064</v>
+        <v>2.8015628103511</v>
       </c>
       <c r="F6" t="n">
-        <v>399.7251791459742</v>
+        <v>449.3662063621945</v>
       </c>
       <c r="G6" t="n">
-        <v>1.988682483313304</v>
+        <v>2.119651916802804</v>
       </c>
       <c r="H6" t="n">
         <v>-0.5</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 29)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -898,54 +898,54 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5.440797372616229</v>
+        <v>9.690298371698749</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S6" t="n">
+        <v>85</v>
+      </c>
+      <c r="T6" t="n">
+        <v>54</v>
+      </c>
+      <c r="U6" t="n">
         <v>73</v>
       </c>
-      <c r="T6" t="n">
-        <v>62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>66</v>
-      </c>
       <c r="V6" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="W6" t="n">
-        <v>58.2089552238806</v>
+        <v>58.01886792452831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1116</v>
+        <v>1130</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.231315009587991</v>
+        <v>-0.5803498245424348</v>
       </c>
       <c r="C7" t="n">
-        <v>0.129382618057009</v>
+        <v>0.3604641000501758</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2342559842448198</v>
+        <v>2.289475661871246</v>
       </c>
       <c r="E7" t="n">
-        <v>1.296064726840112</v>
+        <v>1.305861118498618</v>
       </c>
       <c r="F7" t="n">
-        <v>296.1484198068527</v>
+        <v>362.1455983199157</v>
       </c>
       <c r="G7" t="n">
-        <v>1.473375222919665</v>
+        <v>1.708233954339225</v>
       </c>
       <c r="H7" t="n">
         <v>-0.5</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>(201, 27)</t>
+          <t>(212, 37)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -975,54 +975,54 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10.38773696997275</v>
+        <v>3.738984975484223</v>
       </c>
       <c r="P7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q7" t="n">
+        <v>55</v>
+      </c>
+      <c r="R7" t="n">
+        <v>63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>94</v>
+      </c>
+      <c r="T7" t="n">
         <v>51</v>
       </c>
-      <c r="R7" t="n">
-        <v>62</v>
-      </c>
-      <c r="S7" t="n">
-        <v>83</v>
-      </c>
-      <c r="T7" t="n">
-        <v>44</v>
-      </c>
       <c r="U7" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="W7" t="n">
-        <v>57.71144278606965</v>
+        <v>57.07547169811321</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1130</v>
+        <v>811</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.5803497920887954</v>
+        <v>-0.2546242100158793</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3604641311508038</v>
+        <v>0.04290627187442211</v>
       </c>
       <c r="D8" t="n">
-        <v>2.28947572944957</v>
+        <v>-0.1015649524208972</v>
       </c>
       <c r="E8" t="n">
-        <v>1.305861159781158</v>
+        <v>1.048795160851438</v>
       </c>
       <c r="F8" t="n">
-        <v>293.68081251948</v>
+        <v>355.9142661576282</v>
       </c>
       <c r="G8" t="n">
-        <v>1.461098569748657</v>
+        <v>1.67884087810202</v>
       </c>
       <c r="H8" t="n">
         <v>-0.5</v>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>(201, 37)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1052,54 +1052,54 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3.053381303387969</v>
+        <v>38.12809957051604</v>
       </c>
       <c r="P8" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S8" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="T8" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="U8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V8" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="W8" t="n">
-        <v>57.71144278606965</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>811</v>
+        <v>288</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.2546242100158798</v>
+        <v>-0.07583992964581711</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04290627187442211</v>
+        <v>-0.288437096087221</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1015649524208973</v>
+        <v>0.6190369519895285</v>
       </c>
       <c r="E9" t="n">
-        <v>1.048795160851438</v>
+        <v>1.694591990741122</v>
       </c>
       <c r="F9" t="n">
-        <v>236.2262772706193</v>
+        <v>251.7959573595038</v>
       </c>
       <c r="G9" t="n">
-        <v>1.175255110799101</v>
+        <v>1.187716779997659</v>
       </c>
       <c r="H9" t="n">
         <v>-0.5</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>(201, 31)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1129,57 +1129,57 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>26.39121949907073</v>
+        <v>5.117767083740515</v>
       </c>
       <c r="P9" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S9" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T9" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U9" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="V9" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="W9" t="n">
-        <v>56.71641791044776</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>32</v>
+        <v>1116</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4717589034227129</v>
+        <v>-1.011784388785441</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2865445430127954</v>
+        <v>0.2471880434949603</v>
       </c>
       <c r="D10" t="n">
-        <v>1.99756985189969</v>
+        <v>-0.1058910324052047</v>
       </c>
       <c r="E10" t="n">
-        <v>1.016305209397624</v>
+        <v>1.311161708266124</v>
       </c>
       <c r="F10" t="n">
-        <v>229.3117038829864</v>
+        <v>220.0105477118452</v>
       </c>
       <c r="G10" t="n">
-        <v>1.140854248174062</v>
+        <v>1.037785602414364</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>(201, 10)</t>
+          <t>(212, 27)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1206,57 +1206,57 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2.981420257314473</v>
+        <v>3.198364887480986</v>
       </c>
       <c r="P10" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S10" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T10" t="n">
         <v>48</v>
       </c>
       <c r="U10" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="V10" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="W10" t="n">
-        <v>55.72139303482587</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.7401069446195185</v>
+        <v>-0.7830270571640949</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2864643308536782</v>
+        <v>-0.508661487376036</v>
       </c>
       <c r="D11" t="n">
-        <v>1.069073505157536</v>
+        <v>-0.2447138625329862</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8158824571187417</v>
+        <v>0.571322665474153</v>
       </c>
       <c r="F11" t="n">
-        <v>185.3277954205593</v>
+        <v>189.0125929521162</v>
       </c>
       <c r="G11" t="n">
-        <v>0.922028832938106</v>
+        <v>0.8915688346797935</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>(201, 8)</t>
+          <t>(212, 49)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1283,31 +1283,31 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2.218651446727812</v>
+        <v>2.752774402636635</v>
       </c>
       <c r="P11" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S11" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="U11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V11" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="W11" t="n">
-        <v>57.2139303482587</v>
+        <v>52.83018867924528</v>
       </c>
     </row>
     <row r="12">
@@ -1315,22 +1315,22 @@
         <v>872</v>
       </c>
       <c r="B12" t="n">
-        <v>1.306961621261062</v>
+        <v>1.306961642615121</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4270207402148176</v>
+        <v>0.4270207494295255</v>
       </c>
       <c r="D12" t="n">
-        <v>1.101279983980487</v>
+        <v>1.101279995396658</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7120179498822108</v>
+        <v>0.7120179577085802</v>
       </c>
       <c r="F12" t="n">
-        <v>161.6313307311958</v>
+        <v>158.5348573881058</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8041359737870436</v>
+        <v>0.7478059310759706</v>
       </c>
       <c r="H12" t="n">
         <v>-0.5</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>(201, 24)</t>
+          <t>(212, 24)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1360,57 +1360,57 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.883130953738954</v>
+        <v>0.7512168485372084</v>
       </c>
       <c r="P12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="T12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="U12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="W12" t="n">
-        <v>55.22388059701493</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>878</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
-        <v>0.351498556397795</v>
+        <v>-0.2477645639389803</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03390393877586916</v>
+        <v>0.3729790947000873</v>
       </c>
       <c r="D13" t="n">
-        <v>0.965017654738484</v>
+        <v>1.575801063664704</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6269879987919765</v>
+        <v>0.9423361090441793</v>
       </c>
       <c r="F13" t="n">
-        <v>145.16351237746</v>
+        <v>153.3012430371957</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7222065292410944</v>
+        <v>0.7231190709301683</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>(201, 8)</t>
+          <t>(212, 10)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1437,57 +1437,57 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>20.30155242479139</v>
+        <v>0.938765687421781</v>
       </c>
       <c r="P13" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S13" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="T13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="V13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W13" t="n">
-        <v>57.71144278606965</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>1390</v>
+        <v>878</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.6932879585861633</v>
+        <v>0.3514985338724523</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.6902056896992107</v>
+        <v>0.03390392887195474</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5075357078022835</v>
+        <v>0.9650176391083446</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6641280346508924</v>
+        <v>0.6269879879963958</v>
       </c>
       <c r="F14" t="n">
-        <v>144.6019472600641</v>
+        <v>151.0900306019217</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7194126729356422</v>
+        <v>0.7126888235939701</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 8)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1514,54 +1514,54 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2.042316346666397</v>
+        <v>20.02083290363156</v>
       </c>
       <c r="P14" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S14" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="T14" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="U14" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="V14" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="W14" t="n">
-        <v>55.22388059701493</v>
+        <v>57.07547169811321</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>320</v>
+        <v>504</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.3763213469936971</v>
+        <v>2.259741504024007</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.679443511484252</v>
+        <v>0.4463224204891336</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3067872217751226</v>
+        <v>0.537380097753947</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5996212075370029</v>
+        <v>0.4244056962752481</v>
       </c>
       <c r="F15" t="n">
-        <v>132.8894618964754</v>
+        <v>150.8457782769085</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6611416014750019</v>
+        <v>0.7115366899854173</v>
       </c>
       <c r="H15" t="n">
         <v>-0.5</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>(201, 20)</t>
+          <t>(212, 33)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1591,57 +1591,57 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1.973063382459464</v>
+        <v>0.5942212564755992</v>
       </c>
       <c r="P15" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q15" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S15" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="T15" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="U15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="V15" t="n">
         <v>115</v>
       </c>
       <c r="W15" t="n">
-        <v>57.2139303482587</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1536</v>
+        <v>1390</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2526106788699121</v>
+        <v>-0.693287949860131</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.09342276888731874</v>
+        <v>-0.6902056876304493</v>
       </c>
       <c r="D16" t="n">
-        <v>0.486949360113767</v>
+        <v>-0.5075357067396301</v>
       </c>
       <c r="E16" t="n">
-        <v>0.583026150949884</v>
+        <v>0.6641280424247706</v>
       </c>
       <c r="F16" t="n">
-        <v>132.1648938800327</v>
+        <v>146.2821455776538</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6575367854727996</v>
+        <v>0.6900101206493104</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1668,57 +1668,57 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8.03829262720615</v>
+        <v>1.999716654057415</v>
       </c>
       <c r="P16" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S16" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T16" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="U16" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="V16" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W16" t="n">
-        <v>56.71641791044776</v>
+        <v>54.71698113207547</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>235</v>
+        <v>798</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.7830270391426534</v>
+        <v>-0.8529832118195465</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.508661480100091</v>
+        <v>-0.589456623512797</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2447138562845333</v>
+        <v>-0.1341239046070657</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5713226813387452</v>
+        <v>0.5501731002880618</v>
       </c>
       <c r="F17" t="n">
-        <v>128.8770123131929</v>
+        <v>144.9272789186441</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6411791657372784</v>
+        <v>0.6836192401822834</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>(201, 49)</t>
+          <t>(212, 11)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1745,54 +1745,54 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2.260522352923425</v>
+        <v>2.159744776652666</v>
       </c>
       <c r="P17" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S17" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="T17" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V17" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="W17" t="n">
-        <v>53.23383084577114</v>
+        <v>54.71698113207547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>798</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.8529832118195461</v>
+        <v>-0.5103108969460655</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.589456623512797</v>
+        <v>0.3423567696060337</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1341239046070657</v>
+        <v>0.9194961563669691</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5501731002880611</v>
+        <v>0.7625137190571896</v>
       </c>
       <c r="F18" t="n">
-        <v>127.0667228940532</v>
+        <v>112.8889885593017</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6321727507166823</v>
+        <v>0.53249522905331</v>
       </c>
       <c r="H18" t="n">
         <v>-0.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>(201, 11)</t>
+          <t>(212, 8)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1822,57 +1822,57 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2.072466956006574</v>
+        <v>0.5553810420225597</v>
       </c>
       <c r="P18" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q18" t="n">
+        <v>55</v>
+      </c>
+      <c r="R18" t="n">
+        <v>63</v>
+      </c>
+      <c r="S18" t="n">
+        <v>87</v>
+      </c>
+      <c r="T18" t="n">
         <v>51</v>
       </c>
-      <c r="R18" t="n">
-        <v>62</v>
-      </c>
-      <c r="S18" t="n">
-        <v>79</v>
-      </c>
-      <c r="T18" t="n">
-        <v>55</v>
-      </c>
       <c r="U18" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="V18" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="W18" t="n">
-        <v>55.22388059701493</v>
+        <v>55.66037735849056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>1006</v>
+        <v>222</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.777715839238856</v>
+        <v>-1.467001359729218</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5849557700501804</v>
+        <v>-0.603924989932363</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1616793887510099</v>
+        <v>-0.3780185432578898</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4657549560052323</v>
+        <v>0.1487620086959595</v>
       </c>
       <c r="F19" t="n">
-        <v>104.2700998634057</v>
+        <v>90.10291957026345</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5187567157383368</v>
+        <v>0.4250137715578465</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 20)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1899,75 +1899,75 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1.886830667032886</v>
+        <v>1.703752582924986</v>
       </c>
       <c r="P19" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q19" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T19" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="U19" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="W19" t="n">
-        <v>54.72636815920397</v>
+        <v>53.77358490566038</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>188</v>
+        <v>1444</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.3365863792498627</v>
+        <v>-0.0407761079964169</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6202324521757625</v>
+        <v>-0.05351773379816763</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.06560119926392655</v>
+        <v>-0.3204116209545487</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4281752187083691</v>
+        <v>0.2337549432608508</v>
       </c>
       <c r="F20" t="n">
-        <v>96.73390892648442</v>
+        <v>80.09515712224521</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4812632284899722</v>
+        <v>0.377807344916251</v>
       </c>
       <c r="H20" t="n">
         <v>-0.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>(201, 31)</t>
+          <t>(212, 52)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1976,57 +1976,57 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1.775940096010312</v>
+        <v>8.059479505262358</v>
       </c>
       <c r="P20" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R20" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S20" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="T20" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="U20" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V20" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W20" t="n">
-        <v>58.2089552238806</v>
+        <v>56.13207547169812</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>504</v>
+        <v>286</v>
       </c>
       <c r="B21" t="n">
-        <v>2.259741387705714</v>
+        <v>-0.6929083138764903</v>
       </c>
       <c r="C21" t="n">
-        <v>0.446322380995245</v>
+        <v>-0.3702779184334557</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5373800648757397</v>
+        <v>-0.03914348168694384</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4244056710330369</v>
+        <v>0.1339735170831015</v>
       </c>
       <c r="F21" t="n">
-        <v>94.67175182199611</v>
+        <v>72.05476953115539</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4710037404079409</v>
+        <v>0.3398809883545065</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>(201, 33)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2053,57 +2053,57 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.05529939896282916</v>
+        <v>1.917907796912248</v>
       </c>
       <c r="P21" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q21" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R21" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S21" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="T21" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="U21" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="V21" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="W21" t="n">
-        <v>54.22885572139303</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01530174795194085</v>
+        <v>-0.4969668445654574</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1672041013104723</v>
+        <v>-0.02459951893825462</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4213221520634361</v>
+        <v>0.4938559183090558</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3673192899749068</v>
+        <v>0.2457257743552296</v>
       </c>
       <c r="F22" t="n">
-        <v>83.58304311726155</v>
+        <v>71.58661150021589</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4158360354092615</v>
+        <v>0.3376726957557353</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2130,54 +2130,54 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>3.486996623588305</v>
+        <v>14.7268007802633</v>
       </c>
       <c r="P22" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S22" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="T22" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="U22" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V22" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W22" t="n">
-        <v>57.2139303482587</v>
+        <v>54.71698113207547</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>736</v>
+        <v>1022</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7637935089223692</v>
+        <v>-0.1286581451772187</v>
       </c>
       <c r="C23" t="n">
-        <v>0.03577923962948035</v>
+        <v>0.04545178753173772</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3791091387111946</v>
+        <v>-0.0111488191002914</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3073661331233402</v>
+        <v>0.2714356614399307</v>
       </c>
       <c r="F23" t="n">
-        <v>73.19367522309142</v>
+        <v>65.4915621209114</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3641476379258279</v>
+        <v>0.3089224628344877</v>
       </c>
       <c r="H23" t="n">
         <v>-0.5</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>(201, 14)</t>
+          <t>(212, 11)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2207,75 +2207,75 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>9.177623719699957</v>
+        <v>5.796706567784066</v>
       </c>
       <c r="P23" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q23" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R23" t="n">
+        <v>63</v>
+      </c>
+      <c r="S23" t="n">
+        <v>82</v>
+      </c>
+      <c r="T23" t="n">
+        <v>68</v>
+      </c>
+      <c r="U23" t="n">
         <v>62</v>
       </c>
-      <c r="S23" t="n">
-        <v>89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>37</v>
-      </c>
-      <c r="U23" t="n">
-        <v>75</v>
-      </c>
       <c r="V23" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="W23" t="n">
-        <v>57.2139303482587</v>
+        <v>52.83018867924528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1068</v>
+        <v>1108</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4302018060140065</v>
+        <v>-0.4037581981261786</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3970899856683843</v>
+        <v>-0.2452972604927378</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.01456378783964482</v>
+        <v>-0.2023662931720209</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3120030024448919</v>
+        <v>0.2831630778167512</v>
       </c>
       <c r="F24" t="n">
-        <v>72.52740794218462</v>
+        <v>57.70797122427541</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3608328753342518</v>
+        <v>0.2722074114352614</v>
       </c>
       <c r="H24" t="n">
         <v>-0.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>(201, 29)</t>
+          <t>(212, 54)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2284,57 +2284,57 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>1.908692962193181</v>
+        <v>2.109704245732171</v>
       </c>
       <c r="P24" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q24" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R24" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S24" t="n">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="T24" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="U24" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="V24" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="W24" t="n">
-        <v>54.72636815920397</v>
+        <v>56.13207547169812</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>1108</v>
+        <v>538</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5594326583660566</v>
+        <v>-1.005647437048534</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.4247710897924153</v>
+        <v>-0.6045647710451106</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2517968937846158</v>
+        <v>-0.2899798717588846</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2764035824744018</v>
+        <v>0.05071179522831869</v>
       </c>
       <c r="F25" t="n">
-        <v>69.38834780693077</v>
+        <v>57.09159188736257</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3452156607309989</v>
+        <v>0.2692999617328423</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>(201, 54)</t>
+          <t>(212, 17)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2361,57 +2361,57 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>1.81270987839522</v>
+        <v>1.445444350432963</v>
       </c>
       <c r="P25" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q25" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S25" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="T25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="U25" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="V25" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="W25" t="n">
-        <v>57.2139303482587</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>1124</v>
+        <v>428</v>
       </c>
       <c r="B26" t="n">
-        <v>0.4654098593432531</v>
+        <v>0.4151018901164354</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09365771248463674</v>
+        <v>0.2355751708638039</v>
       </c>
       <c r="D26" t="n">
-        <v>1.095845993100747</v>
+        <v>0.3421538872889486</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2633599597315566</v>
+        <v>0.1244453345472203</v>
       </c>
       <c r="F26" t="n">
-        <v>60.37311219919707</v>
+        <v>53.79395350558867</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3003637422845625</v>
+        <v>0.2537450637056069</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>(201, 74)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2438,57 +2438,57 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>2.207036925376893</v>
+        <v>0.07712991473243079</v>
       </c>
       <c r="P26" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S26" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="T26" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="U26" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V26" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="W26" t="n">
-        <v>54.72636815920397</v>
+        <v>53.30188679245283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>1022</v>
+        <v>736</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.1286581530488442</v>
+        <v>0.7637934788388798</v>
       </c>
       <c r="C27" t="n">
-        <v>0.04545178313414212</v>
+        <v>0.03577922835517512</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.01114882185766637</v>
+        <v>0.3791091273280787</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2714356581949587</v>
+        <v>0.3073661243352784</v>
       </c>
       <c r="F27" t="n">
-        <v>59.32197324411749</v>
+        <v>52.8528473688319</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2951341952443656</v>
+        <v>0.2493058838152448</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>(201, 11)</t>
+          <t>(212, 14)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2515,54 +2515,54 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>5.493346902878031</v>
+        <v>5.967894369895909</v>
       </c>
       <c r="P27" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R27" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S27" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="T27" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="V27" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="W27" t="n">
-        <v>53.73134328358209</v>
+        <v>56.13207547169812</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>312</v>
+        <v>1244</v>
       </c>
       <c r="B28" t="n">
-        <v>2.060186060805565</v>
+        <v>0.3676670426782513</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2670191399406437</v>
+        <v>-0.1556602695183821</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02479897683101484</v>
+        <v>-0.1496348515575622</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2564448318717531</v>
+        <v>0.218395101444997</v>
       </c>
       <c r="F28" t="n">
-        <v>59.13725333846958</v>
+        <v>52.82568822723422</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2942151907386546</v>
+        <v>0.2491777746567652</v>
       </c>
       <c r="H28" t="n">
         <v>-0.5</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>(201, 58)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2592,31 +2592,31 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.1018505669820387</v>
+        <v>2.600779540133968</v>
       </c>
       <c r="P28" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S28" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T28" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U28" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V28" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="W28" t="n">
-        <v>54.22885572139303</v>
+        <v>53.30188679245283</v>
       </c>
     </row>
     <row r="29">
@@ -2624,22 +2624,22 @@
         <v>430</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1310420612229237</v>
+        <v>0.16876028776238</v>
       </c>
       <c r="C29" t="n">
-        <v>0.07330730366832924</v>
+        <v>0.1278669303496679</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3444237023182937</v>
+        <v>0.3048622582769839</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2490351085016073</v>
+        <v>0.2462325700145787</v>
       </c>
       <c r="F29" t="n">
-        <v>57.89022538721775</v>
+        <v>51.86361971609858</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2880110715781978</v>
+        <v>0.2446397156419745</v>
       </c>
       <c r="H29" t="n">
         <v>-0.25</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2669,54 +2669,54 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2.928818237283312</v>
+        <v>0.9132367921320784</v>
       </c>
       <c r="P29" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q29" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R29" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S29" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T29" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="U29" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V29" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="W29" t="n">
-        <v>54.22885572139303</v>
+        <v>53.30188679245283</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>144</v>
+        <v>1344</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.4969668445654577</v>
+        <v>-1.074053701876283</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.02459951893825504</v>
+        <v>-0.7119515664705193</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4938559183090552</v>
+        <v>-0.171706863680007</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2457257743552293</v>
+        <v>0.1499693835933621</v>
       </c>
       <c r="F30" t="n">
-        <v>54.25844700630677</v>
+        <v>50.07960099856484</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2699425224194367</v>
+        <v>0.2362245330120983</v>
       </c>
       <c r="H30" t="n">
         <v>-0.5</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2746,61 +2746,61 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>11.97348785953881</v>
+        <v>1.331798599985074</v>
       </c>
       <c r="P30" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q30" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R30" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S30" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="T30" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U30" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="V30" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="W30" t="n">
-        <v>54.72636815920397</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1444</v>
+        <v>1068</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.04077611365652786</v>
+        <v>0.3627958699018708</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.05351773653251271</v>
+        <v>-0.2398394868794276</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3204116219548642</v>
+        <v>0.0540864392726822</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2337549411410649</v>
+        <v>0.2954452711959914</v>
       </c>
       <c r="F31" t="n">
-        <v>51.51492354580535</v>
+        <v>49.24778898741519</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2562931519691808</v>
+        <v>0.2323008914500717</v>
       </c>
       <c r="H31" t="n">
         <v>-0.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2810,11 +2810,11 @@
         <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>(201, 52)</t>
+          <t>(212, 29)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2823,57 +2823,57 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>5.788938557098344</v>
+        <v>1.968568163952311</v>
       </c>
       <c r="P31" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q31" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R31" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S31" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="T31" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="U31" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="V31" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W31" t="n">
-        <v>56.21890547263681</v>
+        <v>53.77358490566038</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1244</v>
+        <v>96</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3676670445018166</v>
+        <v>-0.6157982996324591</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1556602688680752</v>
+        <v>-0.423335985816666</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1496348511593464</v>
+        <v>-0.03209723291310837</v>
       </c>
       <c r="E32" t="n">
-        <v>0.218395101998302</v>
+        <v>0.09117690555279716</v>
       </c>
       <c r="F32" t="n">
-        <v>48.72589225467803</v>
+        <v>45.57812128486276</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2424173744013832</v>
+        <v>0.2149911381361451</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>(201, 31)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2900,54 +2900,54 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>2.557349066426425</v>
+        <v>1.507849900171849</v>
       </c>
       <c r="P32" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q32" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R32" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S32" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T32" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U32" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="V32" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="W32" t="n">
-        <v>53.73134328358209</v>
+        <v>54.71698113207547</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>222</v>
+        <v>1124</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.142575615678543</v>
+        <v>0.465409875565633</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4168670395741868</v>
+        <v>0.09365771968089774</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2422477508378706</v>
+        <v>1.095846004698069</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2046289316789526</v>
+        <v>0.2633599647544605</v>
       </c>
       <c r="F33" t="n">
-        <v>47.76209612039793</v>
+        <v>45.50416745367187</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2376223687581986</v>
+        <v>0.214642299309773</v>
       </c>
       <c r="H33" t="n">
         <v>-0.5</v>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>(201, 20)</t>
+          <t>(212, 74)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2977,57 +2977,57 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>1.570019565473251</v>
+        <v>1.291773705798979</v>
       </c>
       <c r="P33" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q33" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R33" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S33" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="T33" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="V33" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="W33" t="n">
-        <v>54.22885572139303</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>848</v>
+        <v>224</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1963920488699031</v>
+        <v>-0.02746183203828508</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.04265726318939485</v>
+        <v>-0.2923432632892404</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.03201033208541437</v>
+        <v>0.06365993493743266</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2046679151931022</v>
+        <v>0.1631782042849112</v>
       </c>
       <c r="F34" t="n">
-        <v>46.33388332557078</v>
+        <v>44.62716256285353</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2305168324655263</v>
+        <v>0.210505483787045</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>(201, 10)</t>
+          <t>(212, 20)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3054,31 +3054,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>6.403929254487094</v>
+        <v>1.720062714695682</v>
       </c>
       <c r="P34" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q34" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R34" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S34" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="T34" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="U34" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="V34" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="W34" t="n">
-        <v>54.22885572139303</v>
+        <v>53.30188679245283</v>
       </c>
     </row>
     <row r="35">
@@ -3086,22 +3086,22 @@
         <v>830</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.9497284979862302</v>
+        <v>-0.9497284979862306</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3639086960868848</v>
+        <v>-0.3639086960868855</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03173275385625658</v>
+        <v>0.03173275385625601</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1989841960055267</v>
+        <v>0.1989841960055264</v>
       </c>
       <c r="F35" t="n">
-        <v>45.06736366985777</v>
+        <v>44.54356487032405</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2242157396510337</v>
+        <v>0.2101111550486983</v>
       </c>
       <c r="H35" t="n">
         <v>-0.25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>(201, 7)</t>
+          <t>(212, 7)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3131,57 +3131,57 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>1.616131854121731</v>
+        <v>1.577373273318352</v>
       </c>
       <c r="P35" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q35" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R35" t="n">
+        <v>63</v>
+      </c>
+      <c r="S35" t="n">
+        <v>76</v>
+      </c>
+      <c r="T35" t="n">
+        <v>74</v>
+      </c>
+      <c r="U35" t="n">
         <v>62</v>
       </c>
-      <c r="S35" t="n">
-        <v>74</v>
-      </c>
-      <c r="T35" t="n">
-        <v>67</v>
-      </c>
-      <c r="U35" t="n">
-        <v>60</v>
-      </c>
       <c r="V35" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="W35" t="n">
-        <v>53.23383084577114</v>
+        <v>52.35849056603774</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>624</v>
+        <v>1486</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5449561217506408</v>
+        <v>0.5447858610943705</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1652030391529423</v>
+        <v>0.07199535553553332</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01744686769885514</v>
+        <v>0.08307713609773619</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1872951022256648</v>
+        <v>0.1619361600642397</v>
       </c>
       <c r="F36" t="n">
-        <v>42.26098284802032</v>
+        <v>44.23409005091298</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2102536460100513</v>
+        <v>0.2086513681646839</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3208,57 +3208,57 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2.272698414557627</v>
+        <v>1.898122616558286</v>
       </c>
       <c r="P36" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R36" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S36" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="T36" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="U36" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V36" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="W36" t="n">
-        <v>56.71641791044776</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>940</v>
+        <v>188</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.4012889919723028</v>
+        <v>-0.1854789672994232</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1372232704430253</v>
+        <v>-0.4482276748766224</v>
       </c>
       <c r="D37" t="n">
-        <v>0.09326952053018098</v>
+        <v>0.004698062753131751</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1852696918538955</v>
+        <v>0.3465133665638223</v>
       </c>
       <c r="F37" t="n">
-        <v>42.08824092581887</v>
+        <v>42.88651180449995</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2093942334617854</v>
+        <v>0.2022948670023582</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>(201, 22)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3285,57 +3285,57 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2.525938223056164</v>
+        <v>1.451321679452393</v>
       </c>
       <c r="P37" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R37" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S37" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="T37" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="U37" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="V37" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="W37" t="n">
-        <v>52.7363184079602</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1344</v>
+        <v>940</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.7707852449491687</v>
+        <v>-0.4012889969797729</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5394497008347374</v>
+        <v>-0.1372232731454079</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.07527671355180568</v>
+        <v>0.09326951814991521</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1695991431935332</v>
+        <v>0.1852696897074998</v>
       </c>
       <c r="F38" t="n">
-        <v>39.33934735769805</v>
+        <v>40.9368175449367</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1957181460581992</v>
+        <v>0.1930981959666826</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 22)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3362,31 +3362,31 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>1.362810741678691</v>
+        <v>2.407182553954001</v>
       </c>
       <c r="P38" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q38" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R38" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S38" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="T38" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="U38" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="V38" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="W38" t="n">
-        <v>57.2139303482587</v>
+        <v>51.88679245283019</v>
       </c>
     </row>
     <row r="39">
@@ -3394,25 +3394,25 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.2122342418431137</v>
+        <v>-0.2122342465390761</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07201969137001896</v>
+        <v>0.07201968855412247</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4286902849463055</v>
+        <v>0.4286902820691088</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1582568708653348</v>
+        <v>0.1582568691362782</v>
       </c>
       <c r="F39" t="n">
-        <v>37.40216948939957</v>
+        <v>40.04896719568757</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1860804452208934</v>
+        <v>0.1889102226211678</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>(201, 8)</t>
+          <t>(212, 8)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3439,57 +3439,57 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>1.583743996691948</v>
+        <v>1.623035817201606</v>
       </c>
       <c r="P39" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q39" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S39" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="T39" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="U39" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V39" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="W39" t="n">
-        <v>53.23383084577114</v>
+        <v>52.83018867924528</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>302</v>
+        <v>1150</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.69731860261689</v>
+        <v>-0.03034252368786554</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6350549635865874</v>
+        <v>-0.01314188674484356</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2656630332350596</v>
+        <v>0.07401303558742484</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1549713521000648</v>
+        <v>0.0547160816967866</v>
       </c>
       <c r="F40" t="n">
-        <v>37.00306088351252</v>
+        <v>39.24608833654253</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1840948302662314</v>
+        <v>0.1851230581912383</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>(201, 16)</t>
+          <t>(212, 25)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3516,54 +3516,54 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>1.28988802674106</v>
+        <v>15.08649015057708</v>
       </c>
       <c r="P40" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q40" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R40" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S40" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="T40" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="U40" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="V40" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="W40" t="n">
-        <v>56.21890547263681</v>
+        <v>55.66037735849056</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>286</v>
+        <v>1422</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.4435625427164129</v>
+        <v>-0.9083273785767918</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2174389905937018</v>
+        <v>-0.3273017653187258</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03322527768986381</v>
+        <v>0.1225452168408105</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1647695942969254</v>
+        <v>0.1099439227291289</v>
       </c>
       <c r="F41" t="n">
-        <v>36.42696111695574</v>
+        <v>38.37014067876942</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1812286622734116</v>
+        <v>0.1809912296168369</v>
       </c>
       <c r="H41" t="n">
         <v>-0.25</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 19)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3593,54 +3593,54 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>1.83346901941818</v>
+        <v>1.552979692732754</v>
       </c>
       <c r="P41" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R41" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S41" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="T41" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="U41" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V41" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W41" t="n">
-        <v>54.22885572139303</v>
+        <v>52.35849056603774</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.02746181906916945</v>
+        <v>-0.8047495383218353</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2923432586365131</v>
+        <v>-0.3948169291997625</v>
       </c>
       <c r="D42" t="n">
-        <v>0.06365993973921083</v>
+        <v>0.00258055592359805</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1631782086451997</v>
+        <v>0.1141223515357377</v>
       </c>
       <c r="F42" t="n">
-        <v>36.27371731672054</v>
+        <v>37.7774304796755</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1804662553070673</v>
+        <v>0.1781954267909222</v>
       </c>
       <c r="H42" t="n">
         <v>-0.5</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>(201, 20)</t>
+          <t>(212, 8)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3670,54 +3670,54 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>1.617309446945213</v>
+        <v>1.451336844020592</v>
       </c>
       <c r="P42" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q42" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R42" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S42" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="T42" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="U42" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="V42" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="W42" t="n">
-        <v>53.73134328358209</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1316</v>
+        <v>848</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7606730248468597</v>
+        <v>0.1963920412596173</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1003915968367077</v>
+        <v>-0.04265726650649498</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1143587603080978</v>
+        <v>-0.03201033428443718</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1270600714607411</v>
+        <v>0.2046679127514962</v>
       </c>
       <c r="F43" t="n">
-        <v>30.83770033424639</v>
+        <v>37.56765304240804</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1534213946977432</v>
+        <v>0.1772059105773964</v>
       </c>
       <c r="H43" t="n">
         <v>-0.25</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>(201, 43)</t>
+          <t>(212, 10)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3747,54 +3747,54 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>2.528229448798303</v>
+        <v>5.154178762261176</v>
       </c>
       <c r="P43" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q43" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R43" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S43" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="T43" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="U43" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="V43" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="W43" t="n">
-        <v>54.72636815920397</v>
+        <v>53.30188679245283</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1456</v>
+        <v>154</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.4724414407366854</v>
+        <v>0.07322845339175529</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3818895335382935</v>
+        <v>-0.06175034448523149</v>
       </c>
       <c r="D44" t="n">
-        <v>0.05465301318190948</v>
+        <v>0.3350180514159409</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1237939878299079</v>
+        <v>0.3079554282547646</v>
       </c>
       <c r="F44" t="n">
-        <v>29.90546061436581</v>
+        <v>34.39829348971884</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1487833861411234</v>
+        <v>0.1622561013665983</v>
       </c>
       <c r="H44" t="n">
         <v>-0.25</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>(201, 13)</t>
+          <t>(212, 16)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3824,57 +3824,57 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>1.389597967670419</v>
+        <v>3.62761451323408</v>
       </c>
       <c r="P44" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q44" t="n">
+        <v>55</v>
+      </c>
+      <c r="R44" t="n">
+        <v>63</v>
+      </c>
+      <c r="S44" t="n">
+        <v>94</v>
+      </c>
+      <c r="T44" t="n">
         <v>51</v>
       </c>
-      <c r="R44" t="n">
-        <v>62</v>
-      </c>
-      <c r="S44" t="n">
-        <v>85</v>
-      </c>
-      <c r="T44" t="n">
-        <v>41</v>
-      </c>
       <c r="U44" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="V44" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="W44" t="n">
-        <v>57.2139303482587</v>
+        <v>55.66037735849056</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1038</v>
+        <v>148</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.2879815865865049</v>
+        <v>-0.2106776835639741</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1458736041970225</v>
+        <v>-0.05776385515527295</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.01059916995141142</v>
+        <v>0.2908013751570968</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1029920310823041</v>
+        <v>0.2259571090915757</v>
       </c>
       <c r="F45" t="n">
-        <v>26.99374294374715</v>
+        <v>34.39629875696286</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1342972285758565</v>
+        <v>0.1622466922498248</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>(201, 19)</t>
+          <t>(212, 31)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3901,57 +3901,57 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>1.920641053020597</v>
+        <v>3.808792657860097</v>
       </c>
       <c r="P45" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q45" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R45" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S45" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="T45" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="U45" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V45" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="W45" t="n">
-        <v>56.71641791044776</v>
+        <v>56.13207547169812</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>60</v>
+        <v>272</v>
       </c>
       <c r="B46" t="n">
-        <v>0.7568123179926477</v>
+        <v>-0.1517574622436499</v>
       </c>
       <c r="C46" t="n">
-        <v>0.02193867746724479</v>
+        <v>-0.1488331743527213</v>
       </c>
       <c r="D46" t="n">
-        <v>0.178042021396518</v>
+        <v>-0.03245133136793962</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1051047715918767</v>
+        <v>0.05128624266139908</v>
       </c>
       <c r="F46" t="n">
-        <v>26.11427423963519</v>
+        <v>32.89659059397869</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1299217623862448</v>
+        <v>0.1551725971414089</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>(201, 14)</t>
+          <t>(212, 19)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3978,54 +3978,54 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>4.922041680963792</v>
+        <v>2.042594151581177</v>
       </c>
       <c r="P46" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R46" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S46" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T46" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="U46" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="V46" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="W46" t="n">
-        <v>52.7363184079602</v>
+        <v>54.24528301886793</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1152</v>
+        <v>552</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.1323619893837537</v>
+        <v>-0.4129970092220722</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1821812080403123</v>
+        <v>-0.144654834260073</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2915643157148817</v>
+        <v>-0.115758168897428</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1011687329085016</v>
+        <v>0.05732069603875665</v>
       </c>
       <c r="F47" t="n">
-        <v>25.32149819652165</v>
+        <v>32.63271816680404</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1259776029677694</v>
+        <v>0.1539279158811511</v>
       </c>
       <c r="H47" t="n">
         <v>-0.25</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>(201, 25)</t>
+          <t>(212, 32)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4055,57 +4055,57 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>1.691496144541393</v>
+        <v>2.064104885733761</v>
       </c>
       <c r="P47" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R47" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S47" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="T47" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="U47" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="V47" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W47" t="n">
-        <v>56.71641791044776</v>
+        <v>52.83018867924528</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1262</v>
+        <v>352</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3231349968814814</v>
+        <v>-0.4985802892517043</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.04073676429231483</v>
+        <v>-0.4293087545344865</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09707344678512414</v>
+        <v>-0.04201312539670841</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1048974161138559</v>
+        <v>0.06743936027075378</v>
       </c>
       <c r="F48" t="n">
-        <v>25.05039310369686</v>
+        <v>32.33363746501348</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1246288214114272</v>
+        <v>0.1525171578538372</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>(201, 9)</t>
+          <t>(212, 15)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4132,54 +4132,54 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>4.059369676912189</v>
+        <v>1.355262165616018</v>
       </c>
       <c r="P48" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q48" t="n">
+        <v>55</v>
+      </c>
+      <c r="R48" t="n">
+        <v>63</v>
+      </c>
+      <c r="S48" t="n">
+        <v>93</v>
+      </c>
+      <c r="T48" t="n">
         <v>51</v>
       </c>
-      <c r="R48" t="n">
-        <v>62</v>
-      </c>
-      <c r="S48" t="n">
-        <v>85</v>
-      </c>
-      <c r="T48" t="n">
-        <v>38</v>
-      </c>
       <c r="U48" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="V48" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="W48" t="n">
-        <v>54.72636815920397</v>
+        <v>55.18867924528303</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>538</v>
+        <v>60</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.713684380233351</v>
+        <v>0.7568123562228755</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4305496961202628</v>
+        <v>0.02193869163902832</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1742021451962037</v>
+        <v>0.1780420331105563</v>
       </c>
       <c r="E49" t="n">
-        <v>0.09861989274956358</v>
+        <v>0.1051047799831964</v>
       </c>
       <c r="F49" t="n">
-        <v>24.44908472161646</v>
+        <v>27.19730425012992</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1216372374209774</v>
+        <v>0.1282891709911789</v>
       </c>
       <c r="H49" t="n">
         <v>-0.25</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>(201, 17)</t>
+          <t>(212, 14)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4209,31 +4209,185 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>1.282516138130083</v>
+        <v>4.847621777178182</v>
       </c>
       <c r="P49" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q49" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R49" t="n">
+        <v>63</v>
+      </c>
+      <c r="S49" t="n">
+        <v>78</v>
+      </c>
+      <c r="T49" t="n">
+        <v>72</v>
+      </c>
+      <c r="U49" t="n">
         <v>62</v>
       </c>
-      <c r="S49" t="n">
-        <v>84</v>
-      </c>
-      <c r="T49" t="n">
-        <v>35</v>
-      </c>
-      <c r="U49" t="n">
-        <v>82</v>
-      </c>
       <c r="V49" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="W49" t="n">
-        <v>56.71641791044776</v>
+        <v>52.35849056603774</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.4521688640083241</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.2628700546787339</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.236740638886616</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.003378225223045348</v>
+      </c>
+      <c r="F50" t="n">
+        <v>25.86240264648263</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1219924653135973</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>10</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>(212, 22)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>1.464078974163452</v>
+      </c>
+      <c r="P50" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>55</v>
+      </c>
+      <c r="R50" t="n">
+        <v>63</v>
+      </c>
+      <c r="S50" t="n">
+        <v>66</v>
+      </c>
+      <c r="T50" t="n">
+        <v>66</v>
+      </c>
+      <c r="U50" t="n">
+        <v>80</v>
+      </c>
+      <c r="V50" t="n">
+        <v>109</v>
+      </c>
+      <c r="W50" t="n">
+        <v>51.41509433962265</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>924</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.07575158239418585</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.01602335571755773</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3475549218291498</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.07472548341667093</v>
+      </c>
+      <c r="F51" t="n">
+        <v>23.65607387293355</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1115852541176111</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>10</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>(212, 16)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>neural_networ</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>5.963912933377656</v>
+      </c>
+      <c r="P51" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>55</v>
+      </c>
+      <c r="R51" t="n">
+        <v>63</v>
+      </c>
+      <c r="S51" t="n">
+        <v>92</v>
+      </c>
+      <c r="T51" t="n">
+        <v>40</v>
+      </c>
+      <c r="U51" t="n">
+        <v>80</v>
+      </c>
+      <c r="V51" t="n">
+        <v>118</v>
+      </c>
+      <c r="W51" t="n">
+        <v>55.66037735849056</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
+++ b/data/england/p4_modeling/2024-10-02/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,55 +486,65 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>odd_weight</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_sup_cap</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>X_shape_missing</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>model_name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>% roi_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t># result 1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t># result 0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t># result 2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t># pred 1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t># pred 0</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t># pred 2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t># aciertos</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
@@ -545,22 +555,22 @@
         <v>860</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.01440714299954692</v>
+        <v>0.2307175898754397</v>
       </c>
       <c r="C2" t="n">
-        <v>1.127483283172959</v>
+        <v>1.389113173653133</v>
       </c>
       <c r="D2" t="n">
-        <v>1.186257825024297</v>
+        <v>0.6507094028409661</v>
       </c>
       <c r="E2" t="n">
-        <v>34.93830479936162</v>
+        <v>34.4478478176966</v>
       </c>
       <c r="F2" t="n">
-        <v>15120.22078984523</v>
+        <v>18638.18125378289</v>
       </c>
       <c r="G2" t="n">
-        <v>71.32179617851524</v>
+        <v>84.33566178182303</v>
       </c>
       <c r="H2" t="n">
         <v>-0.5</v>
@@ -570,74 +580,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>40</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>62.25751986122732</v>
-      </c>
-      <c r="P2" t="n">
-        <v>94</v>
-      </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>59.71187242435725</v>
       </c>
       <c r="R2" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S2" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="T2" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="U2" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="V2" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="W2" t="n">
-        <v>59.43396226415094</v>
+        <v>61</v>
+      </c>
+      <c r="X2" t="n">
+        <v>130</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>58.82352941176471</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>432</v>
+        <v>146</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.7939613499550131</v>
+        <v>5.897327517057221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03261273677241519</v>
+        <v>3.393858398541448</v>
       </c>
       <c r="D3" t="n">
-        <v>2.363073006705503</v>
+        <v>2.749798179846665</v>
       </c>
       <c r="E3" t="n">
-        <v>5.28858472948063</v>
+        <v>7.2334132082112</v>
       </c>
       <c r="F3" t="n">
-        <v>1600.358117915456</v>
+        <v>1697.321146482519</v>
       </c>
       <c r="G3" t="n">
-        <v>7.548859046771017</v>
+        <v>7.680186183178819</v>
       </c>
       <c r="H3" t="n">
         <v>-0.5</v>
@@ -647,74 +667,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>230.4696586014843</v>
-      </c>
-      <c r="P3" t="n">
-        <v>94</v>
-      </c>
       <c r="Q3" t="n">
-        <v>55</v>
+        <v>1.262966005440731</v>
       </c>
       <c r="R3" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="T3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U3" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="V3" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="W3" t="n">
-        <v>58.01886792452831</v>
+        <v>58</v>
+      </c>
+      <c r="X3" t="n">
+        <v>128</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>57.9185520361991</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>146</v>
+        <v>1536</v>
       </c>
       <c r="B4" t="n">
-        <v>4.37733775852683</v>
+        <v>0.1174205967912607</v>
       </c>
       <c r="C4" t="n">
-        <v>2.24706489160916</v>
+        <v>-0.2403328784991176</v>
       </c>
       <c r="D4" t="n">
-        <v>4.321306079130742</v>
+        <v>0.2560437319000352</v>
       </c>
       <c r="E4" t="n">
-        <v>4.45470155302961</v>
+        <v>0.4472328521748796</v>
       </c>
       <c r="F4" t="n">
-        <v>1128.249343001611</v>
+        <v>601.0483335585116</v>
       </c>
       <c r="G4" t="n">
-        <v>5.321930863215147</v>
+        <v>2.719675717459328</v>
       </c>
       <c r="H4" t="n">
         <v>-0.5</v>
@@ -724,74 +754,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>(221, 25)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>1.368392155957733</v>
-      </c>
-      <c r="P4" t="n">
-        <v>94</v>
-      </c>
       <c r="Q4" t="n">
-        <v>55</v>
+        <v>12.31628653742153</v>
       </c>
       <c r="R4" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S4" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="T4" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="V4" t="n">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="W4" t="n">
-        <v>58.49056603773585</v>
+        <v>69</v>
+      </c>
+      <c r="X4" t="n">
+        <v>126</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>57.01357466063348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1536</v>
+        <v>811</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1739890298160674</v>
+        <v>-0.3641134607194243</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2301817734925082</v>
+        <v>0.3443976370755928</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4132464390111742</v>
+        <v>-0.4319151425004258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4808518048053221</v>
+        <v>0.778210302233728</v>
       </c>
       <c r="F5" t="n">
-        <v>478.1157967186381</v>
+        <v>447.9829618769835</v>
       </c>
       <c r="G5" t="n">
-        <v>2.255263192069048</v>
+        <v>2.027072225687708</v>
       </c>
       <c r="H5" t="n">
         <v>-0.5</v>
@@ -801,74 +841,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>10.79774878718819</v>
-      </c>
-      <c r="P5" t="n">
-        <v>94</v>
-      </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>4.885848238972616</v>
       </c>
       <c r="R5" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S5" t="n">
+        <v>58</v>
+      </c>
+      <c r="T5" t="n">
+        <v>63</v>
+      </c>
+      <c r="U5" t="n">
         <v>85</v>
       </c>
-      <c r="T5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U5" t="n">
-        <v>67</v>
-      </c>
       <c r="V5" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="W5" t="n">
-        <v>57.54716981132076</v>
+        <v>65</v>
+      </c>
+      <c r="X5" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>56.10859728506787</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>682</v>
+        <v>1130</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1635441466506455</v>
+        <v>-0.6238802330536777</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2439101427985219</v>
+        <v>0.3057062326247876</v>
       </c>
       <c r="D6" t="n">
-        <v>1.129502910787259</v>
+        <v>2.239384912430644</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8015628103511</v>
+        <v>1.292465784962271</v>
       </c>
       <c r="F6" t="n">
-        <v>449.3662063621945</v>
+        <v>409.0194087434823</v>
       </c>
       <c r="G6" t="n">
-        <v>2.119651916802804</v>
+        <v>1.850766555400372</v>
       </c>
       <c r="H6" t="n">
         <v>-0.5</v>
@@ -878,74 +928,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>(212, 29)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>(221, 37)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>9.690298371698749</v>
-      </c>
-      <c r="P6" t="n">
-        <v>94</v>
-      </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>5.054068768928024</v>
       </c>
       <c r="R6" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S6" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="T6" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="U6" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="V6" t="n">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="W6" t="n">
-        <v>58.01886792452831</v>
+        <v>69</v>
+      </c>
+      <c r="X6" t="n">
+        <v>126</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>57.01357466063348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1130</v>
+        <v>682</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5803498245424348</v>
+        <v>0.3069278198902799</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3604641000501758</v>
+        <v>-0.0526899110524667</v>
       </c>
       <c r="D7" t="n">
-        <v>2.289475661871246</v>
+        <v>1.224927783469836</v>
       </c>
       <c r="E7" t="n">
-        <v>1.305861118498618</v>
+        <v>2.577053356475045</v>
       </c>
       <c r="F7" t="n">
-        <v>362.1455983199157</v>
+        <v>357.7666112568258</v>
       </c>
       <c r="G7" t="n">
-        <v>1.708233954339225</v>
+        <v>1.618853444601022</v>
       </c>
       <c r="H7" t="n">
         <v>-0.5</v>
@@ -955,74 +1015,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>(212, 37)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>(221, 29)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>3.738984975484223</v>
-      </c>
-      <c r="P7" t="n">
-        <v>94</v>
-      </c>
       <c r="Q7" t="n">
+        <v>31.72416354981177</v>
+      </c>
+      <c r="R7" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" t="n">
+        <v>58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>63</v>
+      </c>
+      <c r="U7" t="n">
+        <v>89</v>
+      </c>
+      <c r="V7" t="n">
         <v>55</v>
       </c>
-      <c r="R7" t="n">
-        <v>63</v>
-      </c>
-      <c r="S7" t="n">
-        <v>94</v>
-      </c>
-      <c r="T7" t="n">
-        <v>51</v>
-      </c>
-      <c r="U7" t="n">
-        <v>67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>121</v>
-      </c>
       <c r="W7" t="n">
-        <v>57.07547169811321</v>
+        <v>77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>57.46606334841628</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>811</v>
+        <v>288</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.2546242100158793</v>
+        <v>-0.09104138853088074</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04290627187442211</v>
+        <v>-0.3081417460564363</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1015649524208972</v>
+        <v>0.6385287350278185</v>
       </c>
       <c r="E8" t="n">
-        <v>1.048795160851438</v>
+        <v>1.688751185424779</v>
       </c>
       <c r="F8" t="n">
-        <v>355.9142661576282</v>
+        <v>234.6693714765639</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67884087810202</v>
+        <v>1.061852359622461</v>
       </c>
       <c r="H8" t="n">
         <v>-0.5</v>
@@ -1032,151 +1102,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>(221, 25)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O8" t="n">
-        <v>38.12809957051604</v>
-      </c>
-      <c r="P8" t="n">
-        <v>94</v>
-      </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>4.445986703236186</v>
       </c>
       <c r="R8" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="T8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U8" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="V8" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="W8" t="n">
-        <v>56.60377358490566</v>
+        <v>72</v>
+      </c>
+      <c r="X8" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>56.10859728506787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>288</v>
+        <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.07583992964581711</v>
+        <v>-0.3071481314823072</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.288437096087221</v>
+        <v>0.5434581436079093</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6190369519895285</v>
+        <v>1.915053901434881</v>
       </c>
       <c r="E9" t="n">
-        <v>1.694591990741122</v>
+        <v>1.419828668126369</v>
       </c>
       <c r="F9" t="n">
-        <v>251.7959573595038</v>
+        <v>176.5878741850789</v>
       </c>
       <c r="G9" t="n">
-        <v>1.187716779997659</v>
+        <v>0.7990401546836151</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>(221, 10)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>5.117767083740515</v>
-      </c>
-      <c r="P9" t="n">
-        <v>94</v>
-      </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>0.4702883084591358</v>
       </c>
       <c r="R9" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="T9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="U9" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="V9" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="W9" t="n">
-        <v>56.60377358490566</v>
+        <v>73</v>
+      </c>
+      <c r="X9" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>53.39366515837104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1116</v>
+        <v>878</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.011784388785441</v>
+        <v>0.2750049062791879</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2471880434949603</v>
+        <v>0.2605248088513784</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1058910324052047</v>
+        <v>0.359985738821285</v>
       </c>
       <c r="E10" t="n">
-        <v>1.311161708266124</v>
+        <v>0.480510249070489</v>
       </c>
       <c r="F10" t="n">
-        <v>220.0105477118452</v>
+        <v>174.0607799442557</v>
       </c>
       <c r="G10" t="n">
-        <v>1.037785602414364</v>
+        <v>0.7876053391142791</v>
       </c>
       <c r="H10" t="n">
         <v>-0.5</v>
@@ -1186,536 +1276,606 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>(212, 27)</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>(221, 8)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O10" t="n">
-        <v>3.198364887480986</v>
-      </c>
-      <c r="P10" t="n">
-        <v>94</v>
-      </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>2.023149091200694</v>
       </c>
       <c r="R10" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="T10" t="n">
+        <v>63</v>
+      </c>
+      <c r="U10" t="n">
+        <v>99</v>
+      </c>
+      <c r="V10" t="n">
         <v>48</v>
       </c>
-      <c r="U10" t="n">
-        <v>77</v>
-      </c>
-      <c r="V10" t="n">
-        <v>120</v>
-      </c>
       <c r="W10" t="n">
-        <v>56.60377358490566</v>
+        <v>74</v>
+      </c>
+      <c r="X10" t="n">
+        <v>125</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>56.56108597285068</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>235</v>
+        <v>504</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.7830270571640949</v>
+        <v>2.408098464420068</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.508661487376036</v>
+        <v>0.4778805481755828</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2447138625329862</v>
+        <v>0.6046488217049834</v>
       </c>
       <c r="E11" t="n">
-        <v>0.571322665474153</v>
+        <v>0.4568890512018494</v>
       </c>
       <c r="F11" t="n">
-        <v>189.0125929521162</v>
+        <v>162.9471759037743</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8915688346797935</v>
+        <v>0.737317538026128</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>(212, 49)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>(221, 33)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>2.752774402636635</v>
-      </c>
-      <c r="P11" t="n">
-        <v>94</v>
-      </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>0.5428908768959202</v>
       </c>
       <c r="R11" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="T11" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U11" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="V11" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="W11" t="n">
-        <v>52.83018867924528</v>
+        <v>82</v>
+      </c>
+      <c r="X11" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>872</v>
+        <v>1390</v>
       </c>
       <c r="B12" t="n">
-        <v>1.306961642615121</v>
+        <v>-0.5638859323840552</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4270207494295255</v>
+        <v>-0.6431338220608321</v>
       </c>
       <c r="D12" t="n">
-        <v>1.101279995396658</v>
+        <v>-0.4741816093724103</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7120179577085802</v>
+        <v>0.8974560196484321</v>
       </c>
       <c r="F12" t="n">
-        <v>158.5348573881058</v>
+        <v>161.7703552969999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7478059310759706</v>
+        <v>0.7319925579049767</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>(212, 24)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>(221, 25)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>0.7512168485372084</v>
-      </c>
-      <c r="P12" t="n">
-        <v>94</v>
-      </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>2.138165235284018</v>
       </c>
       <c r="R12" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S12" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="T12" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="U12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="V12" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="W12" t="n">
-        <v>54.24528301886793</v>
+        <v>80</v>
+      </c>
+      <c r="X12" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>32</v>
+        <v>1116</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.2477645639389803</v>
+        <v>-0.9295369991711294</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3729790947000873</v>
+        <v>0.3290339397194353</v>
       </c>
       <c r="D13" t="n">
-        <v>1.575801063664704</v>
+        <v>-0.1374905567172795</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9423361090441793</v>
+        <v>1.267832269602816</v>
       </c>
       <c r="F13" t="n">
-        <v>153.3012430371957</v>
+        <v>158.7990658307452</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7231190709301683</v>
+        <v>0.7185478091888925</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>(212, 10)</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>(221, 27)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>0.938765687421781</v>
-      </c>
-      <c r="P13" t="n">
-        <v>94</v>
-      </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>1.183810611761184</v>
       </c>
       <c r="R13" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S13" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="T13" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="U13" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="V13" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="W13" t="n">
-        <v>54.24528301886793</v>
+        <v>79</v>
+      </c>
+      <c r="X13" t="n">
+        <v>123</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>55.65610859728507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>878</v>
+        <v>235</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3514985338724523</v>
+        <v>-0.7721800684542049</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03390392887195474</v>
+        <v>-0.4276332710642252</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9650176391083446</v>
+        <v>-0.22300387131699</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6269879879963958</v>
+        <v>0.6881874412442344</v>
       </c>
       <c r="F14" t="n">
-        <v>151.0900306019217</v>
+        <v>137.4929309643787</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7126888235939701</v>
+        <v>0.6221399591148359</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>20</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>(212, 8)</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>(221, 49)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O14" t="n">
-        <v>20.02083290363156</v>
-      </c>
-      <c r="P14" t="n">
-        <v>94</v>
-      </c>
       <c r="Q14" t="n">
-        <v>55</v>
+        <v>2.454844609182428</v>
       </c>
       <c r="R14" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S14" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="T14" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="U14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="V14" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="W14" t="n">
-        <v>57.07547169811321</v>
+        <v>72</v>
+      </c>
+      <c r="X14" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>51.58371040723983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>504</v>
+        <v>428</v>
       </c>
       <c r="B15" t="n">
-        <v>2.259741504024007</v>
+        <v>0.5825100861860966</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4463224204891336</v>
+        <v>0.3319504753622485</v>
       </c>
       <c r="D15" t="n">
-        <v>0.537380097753947</v>
+        <v>0.3755825086432715</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4244056962752481</v>
+        <v>0.176560851822306</v>
       </c>
       <c r="F15" t="n">
-        <v>150.8457782769085</v>
+        <v>135.3782244593212</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7115366899854173</v>
+        <v>0.6125711513996434</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>(212, 33)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>0.5942212564755992</v>
-      </c>
-      <c r="P15" t="n">
-        <v>94</v>
-      </c>
       <c r="Q15" t="n">
-        <v>55</v>
+        <v>0.8453691043254606</v>
       </c>
       <c r="R15" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S15" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="T15" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="U15" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V15" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="W15" t="n">
-        <v>54.24528301886793</v>
+        <v>75</v>
+      </c>
+      <c r="X15" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>53.39366515837104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>1390</v>
+        <v>798</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.693287949860131</v>
+        <v>-0.9423368473863084</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.6902056876304493</v>
+        <v>-0.610087363480466</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5075357067396301</v>
+        <v>-0.2799872924064887</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6641280424247706</v>
+        <v>0.4817183533691805</v>
       </c>
       <c r="F16" t="n">
-        <v>146.2821455776538</v>
+        <v>122.3271610476927</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6900101206493104</v>
+        <v>0.5535165658266638</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>20</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>(221, 11)</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O16" t="n">
-        <v>1.999716654057415</v>
-      </c>
-      <c r="P16" t="n">
-        <v>94</v>
-      </c>
       <c r="Q16" t="n">
-        <v>55</v>
+        <v>1.907274267522812</v>
       </c>
       <c r="R16" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="T16" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U16" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="V16" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="W16" t="n">
-        <v>54.71698113207547</v>
+        <v>74</v>
+      </c>
+      <c r="X16" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>798</v>
+        <v>222</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.8529832118195465</v>
+        <v>-1.477222001789788</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.589456623512797</v>
+        <v>-0.6094114772390068</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1341239046070657</v>
+        <v>-0.3699647336905359</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5501731002880618</v>
+        <v>0.1662069933494189</v>
       </c>
       <c r="F17" t="n">
-        <v>144.9272789186441</v>
+        <v>121.20981465681</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6836192401822834</v>
+        <v>0.54846069980457</v>
       </c>
       <c r="H17" t="n">
         <v>-0.5</v>
@@ -1725,151 +1885,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>(212, 11)</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>(221, 20)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>2.159744776652666</v>
-      </c>
-      <c r="P17" t="n">
-        <v>94</v>
-      </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>1.899984198343983</v>
       </c>
       <c r="R17" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S17" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U17" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="V17" t="n">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="W17" t="n">
-        <v>54.71698113207547</v>
+        <v>63</v>
+      </c>
+      <c r="X17" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>53.84615384615385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.5103108969460655</v>
+        <v>-0.2821273282792092</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3423567696060337</v>
+        <v>0.2768544797638167</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9194961563669691</v>
+        <v>0.4668298674246775</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7625137190571896</v>
+        <v>0.1402048136051522</v>
       </c>
       <c r="F18" t="n">
-        <v>112.8889885593017</v>
+        <v>110.6013849452687</v>
       </c>
       <c r="G18" t="n">
-        <v>0.53249522905331</v>
+        <v>0.5004587554084559</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>(212, 8)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>(221, 8)</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>0.5553810420225597</v>
-      </c>
-      <c r="P18" t="n">
-        <v>94</v>
-      </c>
       <c r="Q18" t="n">
-        <v>55</v>
+        <v>0.8076599513050864</v>
       </c>
       <c r="R18" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S18" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="T18" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="U18" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="V18" t="n">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="W18" t="n">
-        <v>55.66037735849056</v>
+        <v>66</v>
+      </c>
+      <c r="X18" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>222</v>
+        <v>1244</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.467001359729218</v>
+        <v>0.7995999984392529</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.603924989932363</v>
+        <v>-0.1226642577172574</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3780185432578898</v>
+        <v>-0.2720873941609923</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1487620086959595</v>
+        <v>0.4088021864151899</v>
       </c>
       <c r="F19" t="n">
-        <v>90.10291957026345</v>
+        <v>110.0736236625547</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4250137715578465</v>
+        <v>0.4980706953056772</v>
       </c>
       <c r="H19" t="n">
         <v>-0.5</v>
@@ -1879,228 +2059,258 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>(212, 20)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>1.703752582924986</v>
-      </c>
-      <c r="P19" t="n">
-        <v>94</v>
-      </c>
       <c r="Q19" t="n">
-        <v>55</v>
+        <v>5.060438668725623</v>
       </c>
       <c r="R19" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S19" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="T19" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="V19" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="W19" t="n">
-        <v>53.77358490566038</v>
+        <v>65</v>
+      </c>
+      <c r="X19" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>1444</v>
+        <v>154</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0407761079964169</v>
+        <v>0.0584561936938033</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.05351773379816763</v>
+        <v>-0.1504527027906669</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3204116209545487</v>
+        <v>0.4964741788195151</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2337549432608508</v>
+        <v>0.4263770725273049</v>
       </c>
       <c r="F20" t="n">
-        <v>80.09515712224521</v>
+        <v>102.3876077775624</v>
       </c>
       <c r="G20" t="n">
-        <v>0.377807344916251</v>
+        <v>0.4632923428848978</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>(212, 52)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O20" t="n">
-        <v>8.059479505262358</v>
-      </c>
-      <c r="P20" t="n">
-        <v>94</v>
-      </c>
       <c r="Q20" t="n">
+        <v>4.079322167641627</v>
+      </c>
+      <c r="R20" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" t="n">
+        <v>58</v>
+      </c>
+      <c r="T20" t="n">
+        <v>63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>97</v>
+      </c>
+      <c r="V20" t="n">
         <v>55</v>
       </c>
-      <c r="R20" t="n">
-        <v>63</v>
-      </c>
-      <c r="S20" t="n">
-        <v>93</v>
-      </c>
-      <c r="T20" t="n">
-        <v>46</v>
-      </c>
-      <c r="U20" t="n">
-        <v>73</v>
-      </c>
-      <c r="V20" t="n">
-        <v>119</v>
-      </c>
       <c r="W20" t="n">
-        <v>56.13207547169812</v>
+        <v>69</v>
+      </c>
+      <c r="X20" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>56.10859728506787</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>286</v>
+        <v>144</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.6929083138764903</v>
+        <v>-0.6270049035094587</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3702779184334557</v>
+        <v>-0.1078349041344941</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.03914348168694384</v>
+        <v>0.7073977829773463</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1339735170831015</v>
+        <v>0.2654321049622215</v>
       </c>
       <c r="F21" t="n">
-        <v>72.05476953115539</v>
+        <v>97.67534582855041</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3398809883545065</v>
+        <v>0.4419698906269249</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>15</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O21" t="n">
-        <v>1.917907796912248</v>
-      </c>
-      <c r="P21" t="n">
-        <v>94</v>
-      </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>5.098579158337175</v>
       </c>
       <c r="R21" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S21" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="T21" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U21" t="n">
         <v>83</v>
       </c>
       <c r="V21" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="W21" t="n">
-        <v>54.24528301886793</v>
+        <v>69</v>
+      </c>
+      <c r="X21" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>54.29864253393665</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4969668445654574</v>
+        <v>-0.2769874327046526</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02459951893825462</v>
+        <v>-0.2545752267858585</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4938559183090558</v>
+        <v>-0.09276590781778396</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2457257743552296</v>
+        <v>-0.001342789725490263</v>
       </c>
       <c r="F22" t="n">
-        <v>71.58661150021589</v>
+        <v>89.40708148938046</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3376726957557353</v>
+        <v>0.4045569298162012</v>
       </c>
       <c r="H22" t="n">
         <v>-0.5</v>
@@ -2110,74 +2320,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>(221, 19)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>14.7268007802633</v>
-      </c>
-      <c r="P22" t="n">
-        <v>94</v>
-      </c>
       <c r="Q22" t="n">
-        <v>55</v>
+        <v>2.589144925544947</v>
       </c>
       <c r="R22" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S22" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="T22" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U22" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="V22" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="W22" t="n">
-        <v>54.71698113207547</v>
+        <v>79</v>
+      </c>
+      <c r="X22" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>54.75113122171946</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>1022</v>
+        <v>14</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.1286581451772187</v>
+        <v>-0.3620738967691455</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04545178753173772</v>
+        <v>0.3864632013795634</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0111488191002914</v>
+        <v>0.855136579130647</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2714356614399307</v>
+        <v>0.7870156719510212</v>
       </c>
       <c r="F23" t="n">
-        <v>65.4915621209114</v>
+        <v>86.25833045276502</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3089224628344877</v>
+        <v>0.3903091875690725</v>
       </c>
       <c r="H23" t="n">
         <v>-0.5</v>
@@ -2187,305 +2407,345 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>(212, 11)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>(221, 8)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>5.796706567784066</v>
-      </c>
-      <c r="P23" t="n">
-        <v>94</v>
-      </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>0.009951752652723677</v>
       </c>
       <c r="R23" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S23" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="T23" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="U23" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="V23" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="W23" t="n">
-        <v>52.83018867924528</v>
+        <v>77</v>
+      </c>
+      <c r="X23" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>54.75113122171946</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1108</v>
+        <v>736</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.4037581981261786</v>
+        <v>0.9704777655533854</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.2452972604927378</v>
+        <v>0.06798719005910243</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2023662931720209</v>
+        <v>0.1933134718332711</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2831630778167512</v>
+        <v>0.2716781911197282</v>
       </c>
       <c r="F24" t="n">
-        <v>57.70797122427541</v>
+        <v>80.62472931040122</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2722074114352614</v>
+        <v>0.3648177796850734</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>(212, 54)</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>(221, 14)</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>2.109704245732171</v>
-      </c>
-      <c r="P24" t="n">
-        <v>94</v>
-      </c>
       <c r="Q24" t="n">
-        <v>55</v>
+        <v>4.36597819924505</v>
       </c>
       <c r="R24" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S24" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="T24" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="U24" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="V24" t="n">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="W24" t="n">
-        <v>56.13207547169812</v>
+        <v>80</v>
+      </c>
+      <c r="X24" t="n">
+        <v>123</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>55.65610859728507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>538</v>
+        <v>1022</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.005647437048534</v>
+        <v>-0.1600749025897105</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.6045647710451106</v>
+        <v>0.1598198108071398</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2899798717588846</v>
+        <v>-0.0703109580145348</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05071179522831869</v>
+        <v>0.2845308865569544</v>
       </c>
       <c r="F25" t="n">
-        <v>57.09159188736257</v>
+        <v>67.17101864714309</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2692999617328423</v>
+        <v>0.3039412608468013</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>(212, 17)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>(221, 11)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O25" t="n">
-        <v>1.445444350432963</v>
-      </c>
-      <c r="P25" t="n">
-        <v>94</v>
-      </c>
       <c r="Q25" t="n">
-        <v>55</v>
+        <v>0.9017746255098372</v>
       </c>
       <c r="R25" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S25" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="T25" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="U25" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V25" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="W25" t="n">
-        <v>56.60377358490566</v>
+        <v>64</v>
+      </c>
+      <c r="X25" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>52.03619909502263</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>428</v>
+        <v>352</v>
       </c>
       <c r="B26" t="n">
-        <v>0.4151018901164354</v>
+        <v>-0.7453581047615728</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2355751708638039</v>
+        <v>-0.6002379045536594</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3421538872889486</v>
+        <v>-0.09901979999085436</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1244453345472203</v>
+        <v>0.02670594526607829</v>
       </c>
       <c r="F26" t="n">
-        <v>53.79395350558867</v>
+        <v>59.84343207097888</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2537450637056069</v>
+        <v>0.2707847605021669</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>(221, 15)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O26" t="n">
-        <v>0.07712991473243079</v>
-      </c>
-      <c r="P26" t="n">
-        <v>94</v>
-      </c>
       <c r="Q26" t="n">
-        <v>55</v>
+        <v>1.451129058074938</v>
       </c>
       <c r="R26" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S26" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="T26" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U26" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="V26" t="n">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="W26" t="n">
-        <v>53.30188679245283</v>
+        <v>69</v>
+      </c>
+      <c r="X26" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>55.20361990950227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>736</v>
+        <v>440</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7637934788388798</v>
+        <v>-0.4232912899025479</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03577922835517512</v>
+        <v>-0.2382410115284921</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3791091273280787</v>
+        <v>-0.220830844717963</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3073661243352784</v>
+        <v>0.03731884375124359</v>
       </c>
       <c r="F27" t="n">
-        <v>52.8528473688319</v>
+        <v>54.69912592061419</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2493058838152448</v>
+        <v>0.2475073571068515</v>
       </c>
       <c r="H27" t="n">
         <v>-0.25</v>
@@ -2495,151 +2755,171 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>15</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>(212, 14)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>(221, 22)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O27" t="n">
-        <v>5.967894369895909</v>
-      </c>
-      <c r="P27" t="n">
-        <v>94</v>
-      </c>
       <c r="Q27" t="n">
-        <v>55</v>
+        <v>2.038894838125934</v>
       </c>
       <c r="R27" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S27" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="T27" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="U27" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="V27" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="W27" t="n">
-        <v>56.13207547169812</v>
+        <v>81</v>
+      </c>
+      <c r="X27" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>51.58371040723983</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>1244</v>
+        <v>848</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3676670426782513</v>
+        <v>0.09523724470005447</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1556602695183821</v>
+        <v>-0.08034538789626239</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1496348515575622</v>
+        <v>-0.2403052852719043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.218395101444997</v>
+        <v>0.1909149284844842</v>
       </c>
       <c r="F28" t="n">
-        <v>52.82568822723422</v>
+        <v>53.87197789494124</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2491777746567652</v>
+        <v>0.2437646058594626</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>10</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>(221, 10)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O28" t="n">
-        <v>2.600779540133968</v>
-      </c>
-      <c r="P28" t="n">
-        <v>94</v>
-      </c>
       <c r="Q28" t="n">
-        <v>55</v>
+        <v>4.033958914657283</v>
       </c>
       <c r="R28" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S28" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="T28" t="n">
+        <v>63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>86</v>
+      </c>
+      <c r="V28" t="n">
         <v>67</v>
       </c>
-      <c r="U28" t="n">
-        <v>63</v>
-      </c>
-      <c r="V28" t="n">
-        <v>113</v>
-      </c>
       <c r="W28" t="n">
-        <v>53.30188679245283</v>
+        <v>68</v>
+      </c>
+      <c r="X28" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>430</v>
+        <v>60</v>
       </c>
       <c r="B29" t="n">
-        <v>0.16876028776238</v>
+        <v>0.6909806979215244</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1278669303496679</v>
+        <v>0.01330018814111071</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3048622582769839</v>
+        <v>0.1536598102509561</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2462325700145787</v>
+        <v>0.09600900815682444</v>
       </c>
       <c r="F29" t="n">
-        <v>51.86361971609858</v>
+        <v>52.27420252637071</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2446397156419745</v>
+        <v>0.236534853060501</v>
       </c>
       <c r="H29" t="n">
         <v>-0.25</v>
@@ -2649,74 +2929,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>10</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>(221, 14)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O29" t="n">
-        <v>0.9132367921320784</v>
-      </c>
-      <c r="P29" t="n">
-        <v>94</v>
-      </c>
       <c r="Q29" t="n">
-        <v>55</v>
+        <v>16.78432384195941</v>
       </c>
       <c r="R29" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S29" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="U29" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="V29" t="n">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="W29" t="n">
-        <v>53.30188679245283</v>
+        <v>64</v>
+      </c>
+      <c r="X29" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>52.48868778280544</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>1344</v>
+        <v>148</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.074053701876283</v>
+        <v>-0.1560746087348997</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.7119515664705193</v>
+        <v>-0.03931962767810788</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.171706863680007</v>
+        <v>0.373444469818057</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1499693835933621</v>
+        <v>0.4956181025856954</v>
       </c>
       <c r="F30" t="n">
-        <v>50.07960099856484</v>
+        <v>49.29602002006922</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2362245330120983</v>
+        <v>0.2230589141179603</v>
       </c>
       <c r="H30" t="n">
         <v>-0.5</v>
@@ -2726,74 +3016,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>1.331798599985074</v>
-      </c>
-      <c r="P30" t="n">
-        <v>94</v>
-      </c>
       <c r="Q30" t="n">
-        <v>55</v>
+        <v>6.67296608055507</v>
       </c>
       <c r="R30" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S30" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="T30" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="U30" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="V30" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="W30" t="n">
-        <v>56.60377358490566</v>
+        <v>80</v>
+      </c>
+      <c r="X30" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>55.20361990950227</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>1068</v>
+        <v>224</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3627958699018708</v>
+        <v>-0.1264955236633097</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2398394868794276</v>
+        <v>-0.3760089069304743</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0540864392726822</v>
+        <v>-0.122547608327317</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2954452711959914</v>
+        <v>0.1354125614170221</v>
       </c>
       <c r="F31" t="n">
-        <v>49.24778898741519</v>
+        <v>48.33759582363851</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2323008914500717</v>
+        <v>0.2187221530481381</v>
       </c>
       <c r="H31" t="n">
         <v>-0.5</v>
@@ -2803,51 +3103,61 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>(212, 29)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>(221, 20)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O31" t="n">
-        <v>1.968568163952311</v>
-      </c>
-      <c r="P31" t="n">
-        <v>94</v>
-      </c>
       <c r="Q31" t="n">
-        <v>55</v>
+        <v>1.581694074307077</v>
       </c>
       <c r="R31" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S31" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="T31" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="U31" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="V31" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="W31" t="n">
-        <v>53.77358490566038</v>
+        <v>79</v>
+      </c>
+      <c r="X31" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="32">
@@ -2855,22 +3165,22 @@
         <v>96</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.6157982996324591</v>
+        <v>-0.59769267296773</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.423335985816666</v>
+        <v>-0.4227542980267714</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03209723291310837</v>
+        <v>-0.02751192679712678</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09117690555279716</v>
+        <v>0.08247128074112105</v>
       </c>
       <c r="F32" t="n">
-        <v>45.57812128486276</v>
+        <v>43.37090295860293</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2149911381361451</v>
+        <v>0.1962484296769363</v>
       </c>
       <c r="H32" t="n">
         <v>-0.25</v>
@@ -2880,305 +3190,345 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>10</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O32" t="n">
-        <v>1.507849900171849</v>
-      </c>
-      <c r="P32" t="n">
-        <v>94</v>
-      </c>
       <c r="Q32" t="n">
-        <v>55</v>
+        <v>1.464213919510544</v>
       </c>
       <c r="R32" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S32" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="T32" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U32" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="V32" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="W32" t="n">
-        <v>54.71698113207547</v>
+        <v>68</v>
+      </c>
+      <c r="X32" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>54.29864253393665</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>1124</v>
+        <v>940</v>
       </c>
       <c r="B33" t="n">
-        <v>0.465409875565633</v>
+        <v>-0.3786440916164247</v>
       </c>
       <c r="C33" t="n">
-        <v>0.09365771968089774</v>
+        <v>-0.1189678354047439</v>
       </c>
       <c r="D33" t="n">
-        <v>1.095846004698069</v>
+        <v>0.1273996107609832</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2633599647544605</v>
+        <v>0.2187245308146085</v>
       </c>
       <c r="F33" t="n">
-        <v>45.50416745367187</v>
+        <v>42.02175973297747</v>
       </c>
       <c r="G33" t="n">
-        <v>0.214642299309773</v>
+        <v>0.1901437091989931</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>10</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>(212, 74)</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>(221, 22)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O33" t="n">
-        <v>1.291773705798979</v>
-      </c>
-      <c r="P33" t="n">
-        <v>94</v>
-      </c>
       <c r="Q33" t="n">
-        <v>55</v>
+        <v>2.598278295575436</v>
       </c>
       <c r="R33" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S33" t="n">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="U33" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="V33" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="W33" t="n">
-        <v>54.24528301886793</v>
+        <v>71</v>
+      </c>
+      <c r="X33" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>51.13122171945701</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>224</v>
+        <v>430</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.02746183203828508</v>
+        <v>0.2462922664430903</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2923432632892404</v>
+        <v>0.1764677614288051</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06365993493743266</v>
+        <v>0.3992385456569195</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1631782042849112</v>
+        <v>0.3114165368164831</v>
       </c>
       <c r="F34" t="n">
-        <v>44.62716256285353</v>
+        <v>39.90065969336283</v>
       </c>
       <c r="G34" t="n">
-        <v>0.210505483787045</v>
+        <v>0.1805459714631802</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>(212, 20)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O34" t="n">
-        <v>1.720062714695682</v>
-      </c>
-      <c r="P34" t="n">
-        <v>94</v>
-      </c>
       <c r="Q34" t="n">
-        <v>55</v>
+        <v>0.02311022705425101</v>
       </c>
       <c r="R34" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S34" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="T34" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U34" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="V34" t="n">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="W34" t="n">
-        <v>53.30188679245283</v>
+        <v>75</v>
+      </c>
+      <c r="X34" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>52.48868778280544</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>830</v>
+        <v>1486</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.9497284979862306</v>
+        <v>0.5476449198265396</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3639086960868855</v>
+        <v>0.0428178573405026</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03173275385625601</v>
+        <v>0.01940317591095228</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1989841960055264</v>
+        <v>0.158581240571926</v>
       </c>
       <c r="F35" t="n">
-        <v>44.54356487032405</v>
+        <v>36.58931200494214</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2101111550486983</v>
+        <v>0.1655624977599192</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>10</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>(212, 7)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>(221, 25)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O35" t="n">
-        <v>1.577373273318352</v>
-      </c>
-      <c r="P35" t="n">
-        <v>94</v>
-      </c>
       <c r="Q35" t="n">
-        <v>55</v>
+        <v>2.866669376828183</v>
       </c>
       <c r="R35" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S35" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="T35" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="U35" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="V35" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="W35" t="n">
-        <v>52.35849056603774</v>
+        <v>84</v>
+      </c>
+      <c r="X35" t="n">
+        <v>123</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>55.65610859728507</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>1486</v>
+        <v>1444</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5447858610943705</v>
+        <v>-0.1784652300331248</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07199535553553332</v>
+        <v>-0.1970174807319975</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08307713609773619</v>
+        <v>-0.2704071877906168</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1619361600642397</v>
+        <v>0.1766762534116553</v>
       </c>
       <c r="F36" t="n">
-        <v>44.23409005091298</v>
+        <v>36.14659282410955</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2086513681646839</v>
+        <v>0.163559243548007</v>
       </c>
       <c r="H36" t="n">
         <v>-0.5</v>
@@ -3188,74 +3538,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>(221, 52)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O36" t="n">
-        <v>1.898122616558286</v>
-      </c>
-      <c r="P36" t="n">
-        <v>94</v>
-      </c>
       <c r="Q36" t="n">
-        <v>55</v>
+        <v>1.830176301820123</v>
       </c>
       <c r="R36" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S36" t="n">
+        <v>58</v>
+      </c>
+      <c r="T36" t="n">
+        <v>63</v>
+      </c>
+      <c r="U36" t="n">
         <v>95</v>
       </c>
-      <c r="T36" t="n">
-        <v>36</v>
-      </c>
-      <c r="U36" t="n">
-        <v>81</v>
-      </c>
       <c r="V36" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="W36" t="n">
-        <v>56.60377358490566</v>
+        <v>78</v>
+      </c>
+      <c r="X36" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>54.75113122171946</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>188</v>
+        <v>1068</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.1854789672994232</v>
+        <v>0.3411412518458968</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4482276748766224</v>
+        <v>-0.2556083786407862</v>
       </c>
       <c r="D37" t="n">
-        <v>0.004698062753131751</v>
+        <v>0.05056293385971145</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3465133665638223</v>
+        <v>0.2816681514474547</v>
       </c>
       <c r="F37" t="n">
-        <v>42.88651180449995</v>
+        <v>32.61119305410907</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2022948670023582</v>
+        <v>0.1475619595208555</v>
       </c>
       <c r="H37" t="n">
         <v>-0.5</v>
@@ -3265,74 +3625,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>10</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>(221, 29)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O37" t="n">
-        <v>1.451321679452393</v>
-      </c>
-      <c r="P37" t="n">
-        <v>94</v>
-      </c>
       <c r="Q37" t="n">
-        <v>55</v>
+        <v>1.577297036605473</v>
       </c>
       <c r="R37" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S37" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="T37" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="U37" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="V37" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="W37" t="n">
-        <v>56.60377358490566</v>
+        <v>80</v>
+      </c>
+      <c r="X37" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>940</v>
+        <v>816</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.4012889969797729</v>
+        <v>-0.2032929146011122</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1372232731454079</v>
+        <v>-0.03153084207737123</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09326951814991521</v>
+        <v>-0.2469064319226486</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1852696897074998</v>
+        <v>-0.0003037456563057361</v>
       </c>
       <c r="F38" t="n">
-        <v>40.9368175449367</v>
+        <v>31.89587448657434</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1930981959666826</v>
+        <v>0.1443252239211509</v>
       </c>
       <c r="H38" t="n">
         <v>-0.25</v>
@@ -3342,74 +3712,84 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>(212, 22)</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O38" t="n">
-        <v>2.407182553954001</v>
-      </c>
-      <c r="P38" t="n">
-        <v>94</v>
-      </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>5.577271471754599</v>
       </c>
       <c r="R38" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S38" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="T38" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="U38" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="V38" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="W38" t="n">
-        <v>51.88679245283019</v>
+        <v>78</v>
+      </c>
+      <c r="X38" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>53.39366515837104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>16</v>
+        <v>1150</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.2122342465390761</v>
+        <v>0.02946220555364221</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07201968855412247</v>
+        <v>-0.002881492347384409</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4286902820691088</v>
+        <v>0.09414545765794155</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1582568691362782</v>
+        <v>0.07062584035632227</v>
       </c>
       <c r="F39" t="n">
-        <v>40.04896719568757</v>
+        <v>30.67144620537056</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1889102226211678</v>
+        <v>0.1387848244586903</v>
       </c>
       <c r="H39" t="n">
         <v>-0.25</v>
@@ -3419,305 +3799,345 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>10</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>(212, 8)</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>(221, 25)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>1.623035817201606</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
+        <v>49.16421760920802</v>
+      </c>
+      <c r="R39" t="n">
+        <v>100</v>
+      </c>
+      <c r="S39" t="n">
+        <v>58</v>
+      </c>
+      <c r="T39" t="n">
+        <v>63</v>
+      </c>
+      <c r="U39" t="n">
         <v>94</v>
       </c>
-      <c r="Q39" t="n">
-        <v>55</v>
-      </c>
-      <c r="R39" t="n">
-        <v>63</v>
-      </c>
-      <c r="S39" t="n">
-        <v>82</v>
-      </c>
-      <c r="T39" t="n">
-        <v>66</v>
-      </c>
-      <c r="U39" t="n">
-        <v>64</v>
-      </c>
       <c r="V39" t="n">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="W39" t="n">
-        <v>52.83018867924528</v>
+        <v>69</v>
+      </c>
+      <c r="X39" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>54.75113122171946</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1150</v>
+        <v>188</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.03034252368786554</v>
+        <v>-0.2088409876008532</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.01314188674484356</v>
+        <v>-0.4461042116992665</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07401303558742484</v>
+        <v>0.02651002767301804</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0547160816967866</v>
+        <v>0.3653524657238825</v>
       </c>
       <c r="F40" t="n">
-        <v>39.24608833654253</v>
+        <v>28.62975396824845</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1851230581912383</v>
+        <v>0.1295463980463731</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>10</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>(212, 25)</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>(221, 31)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O40" t="n">
-        <v>15.08649015057708</v>
-      </c>
-      <c r="P40" t="n">
-        <v>94</v>
-      </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>1.290394922641314</v>
       </c>
       <c r="R40" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S40" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="T40" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="U40" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="V40" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="W40" t="n">
-        <v>55.66037735849056</v>
+        <v>85</v>
+      </c>
+      <c r="X40" t="n">
+        <v>123</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>55.65610859728507</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1422</v>
+        <v>1108</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.9083273785767918</v>
+        <v>-0.3563026181937744</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3273017653187258</v>
+        <v>-0.2678951848141912</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1225452168408105</v>
+        <v>-0.1730540072977599</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1099439227291289</v>
+        <v>0.3351019591435944</v>
       </c>
       <c r="F41" t="n">
-        <v>38.37014067876942</v>
+        <v>28.49367647507572</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1809912296168369</v>
+        <v>0.128930662783148</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>10</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>(212, 19)</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>(221, 54)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>1.552979692732754</v>
-      </c>
-      <c r="P41" t="n">
-        <v>94</v>
-      </c>
       <c r="Q41" t="n">
-        <v>55</v>
+        <v>1.481272789104339</v>
       </c>
       <c r="R41" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S41" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="T41" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U41" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="V41" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="W41" t="n">
-        <v>52.35849056603774</v>
+        <v>69</v>
+      </c>
+      <c r="X41" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>55.20361990950227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>158</v>
+        <v>924</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.8047495383218353</v>
+        <v>-0.06649993382558649</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.3948169291997625</v>
+        <v>0.02467855328960709</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00258055592359805</v>
+        <v>0.3811967761869579</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1141223515357377</v>
+        <v>0.1032546606452496</v>
       </c>
       <c r="F42" t="n">
-        <v>37.7774304796755</v>
+        <v>22.81060179758049</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1781954267909222</v>
+        <v>0.103215392749233</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>linear</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>(212, 8)</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>(221, 16)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>1.451336844020592</v>
-      </c>
-      <c r="P42" t="n">
-        <v>94</v>
-      </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>3.182392360604874</v>
       </c>
       <c r="R42" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S42" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="T42" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="U42" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="V42" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="W42" t="n">
-        <v>56.60377358490566</v>
+        <v>84</v>
+      </c>
+      <c r="X42" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>55.20361990950227</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>848</v>
+        <v>552</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1963920412596173</v>
+        <v>-0.4971608743085551</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.04265726650649498</v>
+        <v>-0.1764585020846549</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.03201033428443718</v>
+        <v>-0.1628156784096966</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2046679127514962</v>
+        <v>0.05437279594343302</v>
       </c>
       <c r="F43" t="n">
-        <v>37.56765304240804</v>
+        <v>21.77891728479077</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1772059105773964</v>
+        <v>0.09854713703525234</v>
       </c>
       <c r="H43" t="n">
         <v>-0.25</v>
@@ -3727,667 +4147,61 @@
           <t>linear</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>10</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>(212, 10)</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>(221, 32)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>neural_networ</t>
         </is>
       </c>
-      <c r="O43" t="n">
-        <v>5.154178762261176</v>
-      </c>
-      <c r="P43" t="n">
-        <v>94</v>
-      </c>
       <c r="Q43" t="n">
-        <v>55</v>
+        <v>1.558472025269573</v>
       </c>
       <c r="R43" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="S43" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="T43" t="n">
         <v>63</v>
       </c>
       <c r="U43" t="n">
+        <v>84</v>
+      </c>
+      <c r="V43" t="n">
         <v>66</v>
       </c>
-      <c r="V43" t="n">
-        <v>113</v>
-      </c>
       <c r="W43" t="n">
-        <v>53.30188679245283</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0.07322845339175529</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.06175034448523149</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.3350180514159409</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.3079554282547646</v>
-      </c>
-      <c r="F44" t="n">
-        <v>34.39829348971884</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.1622561013665983</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>10</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>3.62761451323408</v>
-      </c>
-      <c r="P44" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>55</v>
-      </c>
-      <c r="R44" t="n">
-        <v>63</v>
-      </c>
-      <c r="S44" t="n">
-        <v>94</v>
-      </c>
-      <c r="T44" t="n">
-        <v>51</v>
-      </c>
-      <c r="U44" t="n">
-        <v>67</v>
-      </c>
-      <c r="V44" t="n">
-        <v>118</v>
-      </c>
-      <c r="W44" t="n">
-        <v>55.66037735849056</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B45" t="n">
-        <v>-0.2106776835639741</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.05776385515527295</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.2908013751570968</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.2259571090915757</v>
-      </c>
-      <c r="F45" t="n">
-        <v>34.39629875696286</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.1622466922498248</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>(212, 31)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>3.808792657860097</v>
-      </c>
-      <c r="P45" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>55</v>
-      </c>
-      <c r="R45" t="n">
-        <v>63</v>
-      </c>
-      <c r="S45" t="n">
-        <v>99</v>
-      </c>
-      <c r="T45" t="n">
-        <v>37</v>
-      </c>
-      <c r="U45" t="n">
-        <v>76</v>
-      </c>
-      <c r="V45" t="n">
-        <v>119</v>
-      </c>
-      <c r="W45" t="n">
-        <v>56.13207547169812</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>272</v>
-      </c>
-      <c r="B46" t="n">
-        <v>-0.1517574622436499</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.1488331743527213</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-0.03245133136793962</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.05128624266139908</v>
-      </c>
-      <c r="F46" t="n">
-        <v>32.89659059397869</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.1551725971414089</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>10</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>(212, 19)</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>2.042594151581177</v>
-      </c>
-      <c r="P46" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>55</v>
-      </c>
-      <c r="R46" t="n">
-        <v>63</v>
-      </c>
-      <c r="S46" t="n">
-        <v>78</v>
-      </c>
-      <c r="T46" t="n">
-        <v>56</v>
-      </c>
-      <c r="U46" t="n">
-        <v>78</v>
-      </c>
-      <c r="V46" t="n">
+        <v>71</v>
+      </c>
+      <c r="X43" t="n">
         <v>115</v>
       </c>
-      <c r="W46" t="n">
-        <v>54.24528301886793</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>552</v>
-      </c>
-      <c r="B47" t="n">
-        <v>-0.4129970092220722</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.144654834260073</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.115758168897428</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.05732069603875665</v>
-      </c>
-      <c r="F47" t="n">
-        <v>32.63271816680404</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.1539279158811511</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>10</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>(212, 32)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>2.064104885733761</v>
-      </c>
-      <c r="P47" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>55</v>
-      </c>
-      <c r="R47" t="n">
-        <v>63</v>
-      </c>
-      <c r="S47" t="n">
-        <v>81</v>
-      </c>
-      <c r="T47" t="n">
-        <v>63</v>
-      </c>
-      <c r="U47" t="n">
-        <v>68</v>
-      </c>
-      <c r="V47" t="n">
-        <v>112</v>
-      </c>
-      <c r="W47" t="n">
-        <v>52.83018867924528</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>352</v>
-      </c>
-      <c r="B48" t="n">
-        <v>-0.4985802892517043</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.4293087545344865</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-0.04201312539670841</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.06743936027075378</v>
-      </c>
-      <c r="F48" t="n">
-        <v>32.33363746501348</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.1525171578538372</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>10</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>(212, 15)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>1.355262165616018</v>
-      </c>
-      <c r="P48" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>55</v>
-      </c>
-      <c r="R48" t="n">
-        <v>63</v>
-      </c>
-      <c r="S48" t="n">
-        <v>93</v>
-      </c>
-      <c r="T48" t="n">
-        <v>51</v>
-      </c>
-      <c r="U48" t="n">
-        <v>68</v>
-      </c>
-      <c r="V48" t="n">
-        <v>117</v>
-      </c>
-      <c r="W48" t="n">
-        <v>55.18867924528303</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.7568123562228755</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.02193869163902832</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.1780420331105563</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.1051047799831964</v>
-      </c>
-      <c r="F49" t="n">
-        <v>27.19730425012992</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.1282891709911789</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>10</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>(212, 14)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>4.847621777178182</v>
-      </c>
-      <c r="P49" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>55</v>
-      </c>
-      <c r="R49" t="n">
-        <v>63</v>
-      </c>
-      <c r="S49" t="n">
-        <v>78</v>
-      </c>
-      <c r="T49" t="n">
-        <v>72</v>
-      </c>
-      <c r="U49" t="n">
-        <v>62</v>
-      </c>
-      <c r="V49" t="n">
-        <v>111</v>
-      </c>
-      <c r="W49" t="n">
-        <v>52.35849056603774</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>440</v>
-      </c>
-      <c r="B50" t="n">
-        <v>-0.4521688640083241</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.2628700546787339</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.236740638886616</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.003378225223045348</v>
-      </c>
-      <c r="F50" t="n">
-        <v>25.86240264648263</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.1219924653135973</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>(212, 22)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>1.464078974163452</v>
-      </c>
-      <c r="P50" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>55</v>
-      </c>
-      <c r="R50" t="n">
-        <v>63</v>
-      </c>
-      <c r="S50" t="n">
-        <v>66</v>
-      </c>
-      <c r="T50" t="n">
-        <v>66</v>
-      </c>
-      <c r="U50" t="n">
-        <v>80</v>
-      </c>
-      <c r="V50" t="n">
-        <v>109</v>
-      </c>
-      <c r="W50" t="n">
-        <v>51.41509433962265</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>924</v>
-      </c>
-      <c r="B51" t="n">
-        <v>-0.07575158239418585</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.01602335571755773</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.3475549218291498</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.07472548341667093</v>
-      </c>
-      <c r="F51" t="n">
-        <v>23.65607387293355</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.1115852541176111</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>10</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>(212, 16)</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>neural_networ</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>5.963912933377656</v>
-      </c>
-      <c r="P51" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>55</v>
-      </c>
-      <c r="R51" t="n">
-        <v>63</v>
-      </c>
-      <c r="S51" t="n">
-        <v>92</v>
-      </c>
-      <c r="T51" t="n">
-        <v>40</v>
-      </c>
-      <c r="U51" t="n">
-        <v>80</v>
-      </c>
-      <c r="V51" t="n">
-        <v>118</v>
-      </c>
-      <c r="W51" t="n">
-        <v>55.66037735849056</v>
+      <c r="Y43" t="n">
+        <v>52.03619909502263</v>
       </c>
     </row>
   </sheetData>
